--- a/hasil_scrapping/2026-09-22/all_2026-09-22.xlsx
+++ b/hasil_scrapping/2026-09-22/all_2026-09-22.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K219"/>
+  <dimension ref="A1:K264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,7 @@
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="51" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -538,7 +538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>kelapa, sawit</t>
+          <t>kelapa, sawit, cpo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>rumput laut</t>
+          <t>rumput laut, biodiesel</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1912,7 +1912,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46287.75965277778</v>
+        <v>46287.57358796296</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>https://garuda.kemdiktisaintek.go.id/documents/detail/6624037</t>
+          <t>https://garuda.kemdiktisaintek.go.id/author/view/10599601</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>rumput laut</t>
+          <t>rumput laut, atsiri, bioethanol</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>pulp, industri agro, kertas, pejabat_kemenperin</t>
+          <t>pulp, industri agro, kertas, pejabat_kemenperin, pejabat_presisi</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2480,26 +2480,26 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46287.25645833334</v>
+        <v>46287.36875</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Garuda - Garba Rujukan Digital</t>
+          <t>Dinilai Mengancam Ekosistem, 50 Ton Ikan Sapu-sapu di Bendung Karet Juwana Pati Dikubur</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>https://garuda.kemdiktisaintek.go.id/documents/detail/6307087</t>
+          <t>https://regional.kompas.com/read/2026/09/22/155115778/dinilai-mengancam-ekosistem-50-ton-ikan-sapu-sapu-di-bendung-karet-juwana</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Garuda - Garba Rujukan Digital</t>
+          <t>Kompas.com</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>atsiri</t>
+          <t>karet</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2527,26 +2527,26 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46287.36875</v>
+        <v>46287.28472222222</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dinilai Mengancam Ekosistem, 50 Ton Ikan Sapu-sapu di Bendung Karet Juwana Pati Dikubur</t>
+          <t>Pekan Ini, Harga Karet di Kuansing Capai Rp22.018 per Kg</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>https://regional.kompas.com/read/2026/09/22/155115778/dinilai-mengancam-ekosistem-50-ton-ikan-sapu-sapu-di-bendung-karet-juwana</t>
+          <t>https://www.goriau.com/berita/baca/pekan-ini-harga-karet-di-kuansing-capai-rp22018-per-kg.html</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Kompas.com</t>
+          <t>GoRiau.com</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -2574,21 +2574,21 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46287.28472222222</v>
+        <v>46287.41130787037</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pekan Ini, Harga Karet di Kuansing Capai Rp22.018 per Kg</t>
+          <t>Suplai Air di 8 Kecamatan Makassar Diprediksi Meningkat Jika Bendung Karet Sungai Tello Dibangun</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>https://www.goriau.com/berita/baca/pekan-ini-harga-karet-di-kuansing-capai-rp22018-per-kg.html</t>
+          <t>https://makassar.tribunnews.com/makassar/1851611/suplai-air-di-8-kecamatan-makassar-diprediksi-meningkat-jika-bendung-karet-sungai-tello-dibangun</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GoRiau.com</t>
+          <t>Tribun-timur.com</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2621,21 +2621,21 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46287.41130787037</v>
+        <v>46287.64778935185</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Suplai Air di 8 Kecamatan Makassar Diprediksi Meningkat Jika Bendung Karet Sungai Tello Dibangun</t>
+          <t>Unit Riset Sungei Putih terima kunjungan Subdenpom I/1-3 Lubuk Pakam sinergi kelembagaan</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>https://makassar.tribunnews.com/makassar/1851611/suplai-air-di-8-kecamatan-makassar-diprediksi-meningkat-jika-bendung-karet-sungai-tello-dibangun</t>
+          <t>https://sumut.antaranews.com/berita/671113/unit-riset-sungei-putih-terima-kunjungan-subdenpom-i-1-3-lubuk-pakam-sinergi-kelembagaan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tribun-timur.com</t>
+          <t>ANTARA News Sumatera Utara</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2668,26 +2668,26 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46287.64778935185</v>
+        <v>46287.35640046297</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Unit Riset Sungei Putih terima kunjungan Subdenpom I/1-3 Lubuk Pakam sinergi kelembagaan</t>
+          <t>Ancaman Denda Rp 7 Juta untuk Angkat Kaki di Bus Singapura</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>https://sumut.antaranews.com/berita/671113/unit-riset-sungei-putih-terima-kunjungan-subdenpom-i-1-3-lubuk-pakam-sinergi-kelembagaan</t>
+          <t>https://www.kompas.id/artikel/ancaman-denda-rp-7-juta-untuk-angkat-kaki-di-bus-singapura?open_from=Section_Berita</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ANTARA News Sumatera Utara</t>
+          <t>Kompas.id</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -2715,26 +2715,26 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46287.35640046297</v>
+        <v>46287.29513888889</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ancaman Denda Rp 7 Juta untuk Angkat Kaki di Bus Singapura</t>
+          <t>Ban Motor Masih Tebal tapi Sudah Tua, Haruskah Diganti?</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompas.id/artikel/ancaman-denda-rp-7-juta-untuk-angkat-kaki-di-bus-singapura?open_from=Section_Berita</t>
+          <t>https://www.idntimes.com/automotive/motorbike/ban-motor-masih-tebal-tapi-sudah-tua-haruskah-diganti-c1c2-01-spf5w-x5vkck</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kompas.id</t>
+          <t>IDN Times</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -2762,16 +2762,16 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46287.29513888889</v>
+        <v>46287.25347222222</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ban Motor Masih Tebal tapi Sudah Tua, Haruskah Diganti?</t>
+          <t>Ban Motor Jarang Dipakai Tetap Bisa Rusak, Kok Bisa?</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>https://www.idntimes.com/automotive/motorbike/ban-motor-masih-tebal-tapi-sudah-tua-haruskah-diganti-c1c2-01-spf5w-x5vkck</t>
+          <t>https://www.idntimes.com/automotive/motorbike/ban-motor-jarang-dipakai-tetap-bisa-rusak-kok-bisa-c1c2-01-spf5w-hflp25</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -2809,26 +2809,26 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46287.25347222222</v>
+        <v>46287.52623842593</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ban Motor Jarang Dipakai Tetap Bisa Rusak, Kok Bisa?</t>
+          <t>50 Ton Ikan Sapu-Sapu dari Bendungan Pati Dikubur Biar tak Dikonsumsi Warga dan Cegah Bau Busuk</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>https://www.idntimes.com/automotive/motorbike/ban-motor-jarang-dipakai-tetap-bisa-rusak-kok-bisa-c1c2-01-spf5w-hflp25</t>
+          <t>https://rejogja.republika.co.id/berita/tlrn2z282/50-ton-ikan-sapusapu-dari-bendungan-pati-dikubur-biar-tak-dikonsumsi-warga-dan-cegah-bau-busuk</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IDN Times</t>
+          <t>republika.co.id</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -2856,21 +2856,21 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46287.52623842593</v>
+        <v>46287.43541666667</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>50 Ton Ikan Sapu-Sapu dari Bendungan Pati Dikubur Biar tak Dikonsumsi Warga dan Cegah Bau Busuk</t>
+          <t>Kenapa Ban Motor Bisa Retak-Retak Meski Jarang Dipakai?</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>https://rejogja.republika.co.id/berita/tlrn2z282/50-ton-ikan-sapusapu-dari-bendungan-pati-dikubur-biar-tak-dikonsumsi-warga-dan-cegah-bau-busuk</t>
+          <t>https://www.idntimes.com/automotive/motorbike/kenapa-ban-motor-bisa-retak-retak-meski-jarang-dipakai-c1c2-01-spf5w-90qsh8</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>republika.co.id</t>
+          <t>IDN Times</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2903,26 +2903,26 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46287.43541666667</v>
+        <v>46287.51854166666</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kenapa Ban Motor Bisa Retak-Retak Meski Jarang Dipakai?</t>
+          <t>Awal Pekan, Harga Karet Kembali Naik ke Level Rp42 Ribuan per Kilogram</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>https://www.idntimes.com/automotive/motorbike/kenapa-ban-motor-bisa-retak-retak-meski-jarang-dipakai-c1c2-01-spf5w-90qsh8</t>
+          <t>https://palembang.tribunnews.com/bisnis/1329488/awal-pekan-harga-karet-kembali-naik-ke-level-rp42-ribuan-per-kilogram</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>IDN Times</t>
+          <t>Sripoku.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -2950,26 +2950,26 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46287.51854166666</v>
+        <v>46287.51038194444</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Awal Pekan, Harga Karet Kembali Naik ke Level Rp42 Ribuan per Kilogram</t>
+          <t>Bea Cukai Makassar pantau harga rokok</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>https://palembang.tribunnews.com/bisnis/1329488/awal-pekan-harga-karet-kembali-naik-ke-level-rp42-ribuan-per-kilogram</t>
+          <t>https://makassar.antaranews.com/berita/638785/bea-cukai-makassar-pantau-harga-rokok</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sripoku.com</t>
+          <t>ANTARA News Makassar</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>karet</t>
+          <t>hasil tembakau</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -2997,26 +2997,26 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46287.51038194444</v>
+        <v>46287.5037962963</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bea Cukai Makassar pantau harga rokok</t>
+          <t>Sosialisasi Dana Bagi Hasil Cukai Hasil Tembakau (DBHCHT) Pemberantasan Peredaran Rokok Ilegal di Kabupaten Sleman</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>https://makassar.antaranews.com/berita/638785/bea-cukai-makassar-pantau-harga-rokok</t>
+          <t>https://satpolpp.slemankab.go.id/sosialisasi-dana-bagi-hasil-cukai-hasil-tembakau-dbhcht-pemberantasan-peredaran-rokok-ilegal-di-kabupaten-sleman/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ANTARA News Makassar</t>
+          <t>satuan polisi pamong praja kabupaten sleman</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -3044,26 +3044,26 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46287.5037962963</v>
+        <v>46287.59711805556</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sosialisasi Dana Bagi Hasil Cukai Hasil Tembakau (DBHCHT) Pemberantasan Peredaran Rokok Ilegal di Kabupaten Sleman</t>
+          <t>Harga Kakao Kering di Aceh Tenggara Turun Rp 1.000/Kg Hari Ini 22 September 2026</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>https://satpolpp.slemankab.go.id/sosialisasi-dana-bagi-hasil-cukai-hasil-tembakau-dbhcht-pemberantasan-peredaran-rokok-ilegal-di-kabupaten-sleman/</t>
+          <t>https://gayo.tribunnews.com/aceh-tenggara/54322/harga-kakao-kering-di-aceh-tenggara-turun-rp-1000kg-hari-ini-22-september-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>satuan polisi pamong praja kabupaten sleman</t>
+          <t>tribungayo.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>hasil tembakau</t>
+          <t>kakao</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3091,21 +3091,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46287.59711805556</v>
+        <v>46287.58871527778</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Harga Kakao Kering di Aceh Tenggara Turun Rp 1.000/Kg Hari Ini 22 September 2026</t>
+          <t>BRMP Sulteng Pastikan Kesiapan Lubang Tanam untuk Percepatan Hilirisasi Kakao di Parigi Moutong</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>https://gayo.tribunnews.com/aceh-tenggara/54322/harga-kakao-kering-di-aceh-tenggara-turun-rp-1000kg-hari-ini-22-september-2026</t>
+          <t>https://sulteng.brmp.pertanian.go.id/berita/brmp-sulteng-pastikan-kesiapan-lubang-tanam-untuk-percepatan-hilirisasi-kakao-di-parigi-moutong</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tribungayo.com</t>
+          <t>pertanian.go.id</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3138,21 +3138,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46287.58871527778</v>
+        <v>46287.48680555556</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BRMP Sulteng Pastikan Kesiapan Lubang Tanam untuk Percepatan Hilirisasi Kakao di Parigi Moutong</t>
+          <t>Bolehkah Anda Mengonsumsi Cokelat Jika Menderita Asam Lambung Naik (Refluks Asam)?</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>https://sulteng.brmp.pertanian.go.id/berita/brmp-sulteng-pastikan-kesiapan-lubang-tanam-untuk-percepatan-hilirisasi-kakao-di-parigi-moutong</t>
+          <t>https://olret.viva.co.id/kesehatan/31391-bolehkah-anda-mengonsumsi-cokelat-jika-menderita-asam-lambung-naik-refluks-asam</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>pertanian.go.id</t>
+          <t>VIVA Olret</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>kakao</t>
+          <t>cokelat</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3185,21 +3185,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46287.48680555556</v>
+        <v>46287.49375</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bolehkah Anda Mengonsumsi Cokelat Jika Menderita Asam Lambung Naik (Refluks Asam)?</t>
+          <t>Sensasi Manis Puddle Cake Singapura: Kue Cokelat Unik ala Film 'Matilda' yang Menggugah Selera</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>https://olret.viva.co.id/kesehatan/31391-bolehkah-anda-mengonsumsi-cokelat-jika-menderita-asam-lambung-naik-refluks-asam</t>
+          <t>https://wisata.viva.co.id/wisata/30493-sensasi-manis-puddle-cake-singapura-kue-cokelat-unik-ala-film-matilda-yang-menggugah-selera</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VIVA Olret</t>
+          <t>VIVA.co.id</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3232,21 +3232,21 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46287.49375</v>
+        <v>46287.30842592593</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sensasi Manis Puddle Cake Singapura: Kue Cokelat Unik ala Film 'Matilda' yang Menggugah Selera</t>
+          <t>Viral Penampakan Bukit Kebo Balikpapan, Berubah Cokelat Saat Kemarau</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>https://wisata.viva.co.id/wisata/30493-sensasi-manis-puddle-cake-singapura-kue-cokelat-unik-ala-film-matilda-yang-menggugah-selera</t>
+          <t>https://kaltim.tribunnews.com/tribun-etam/1167107/viral-penampakan-bukit-kebo-balikpapan-berubah-cokelat-saat-kemarau</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VIVA.co.id</t>
+          <t>Tribunkaltim.co</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3279,26 +3279,26 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46287.30842592593</v>
+        <v>46287.25913366898</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Viral Penampakan Bukit Kebo Balikpapan, Berubah Cokelat Saat Kemarau</t>
+          <t>Banyak Tahi Lalat Tidak Selalu Berbahaya, Tapi Perhatikan 5 Perubahan Ini</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>https://kaltim.tribunnews.com/tribun-etam/1167107/viral-penampakan-bukit-kebo-balikpapan-berubah-cokelat-saat-kemarau</t>
+          <t>https://balinews.id/banyak-tahi-lalat-tidak-selalu-berbahaya-tapi-perhatikan-5-perubahan-ini/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tribunkaltim.co</t>
+          <t>balinews.id</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -3320,27 +3320,27 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>RSS</t>
+          <t>Exa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46287.25913366898</v>
+        <v>46287.21652777777</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Banyak Tahi Lalat Tidak Selalu Berbahaya, Tapi Perhatikan 5 Perubahan Ini</t>
+          <t>Inovasi Rumah Cokelat</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>https://balinews.id/banyak-tahi-lalat-tidak-selalu-berbahaya-tapi-perhatikan-5-perubahan-ini/</t>
+          <t>https://ecampus.bungabangsacirebon.ac.id/iaibbc/repository/item/2729283</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>balinews.id</t>
+          <t>ecampus.bungabangsacirebon.ac.id</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3367,32 +3367,32 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Exa</t>
+          <t>RSS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46287.21652777777</v>
+        <v>46287.38663194444</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Inovasi Rumah Cokelat</t>
+          <t>Bupati Minta Empat Raperda Prakarsa DPRD Purbalingga Disesuaikan</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>https://ecampus.bungabangsacirebon.ac.id/iaibbc/repository/item/2729283</t>
+          <t>https://jatengprov.go.id/beritadaerah/bupati-minta-empat-raperda-prakarsa-dprd-purbalingga-disesuaikan/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ecampus.bungabangsacirebon.ac.id</t>
+          <t>Pemerintah Provinsi Jawa Tengah</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>cokelat</t>
+          <t>minuman beralkohol</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3420,26 +3420,26 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46287.38663194444</v>
+        <v>46287.1165625</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bupati Minta Empat Raperda Prakarsa DPRD Purbalingga Disesuaikan</t>
+          <t>DPRD Madiun Dorong Sanksi Tegas bagi Outlet Miras Tak Berizin</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>https://jatengprov.go.id/beritadaerah/bupati-minta-empat-raperda-prakarsa-dprd-purbalingga-disesuaikan/</t>
+          <t>https://beritajatim.com/dprd-madiun-dorong-sanksi-tegas-bagi-outlet-miras-tak-berizin</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Pemerintah Provinsi Jawa Tengah</t>
+          <t>beritajatim.com</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -3467,16 +3467,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46287.1165625</v>
+        <v>46287.67699074074</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DPRD Madiun Dorong Sanksi Tegas bagi Outlet Miras Tak Berizin</t>
+          <t>Ada 42 Izin Jual Minol Diterbitkan Pemkot Malang, PKS Minta Setop</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>https://beritajatim.com/dprd-madiun-dorong-sanksi-tegas-bagi-outlet-miras-tak-berizin</t>
+          <t>https://beritajatim.com/ada-42-izin-jual-minol-diterbitkan-pemkot-malang-pks-minta-setop</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3514,26 +3514,26 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46287.67699074074</v>
+        <v>46287.29403935185</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ada 42 Izin Jual Minol Diterbitkan Pemkot Malang, PKS Minta Setop</t>
+          <t>BAIS TNI dan Aparat Gabungan Gagalkan Upaya Penyelundupan Miras di PLBN Mota’ain</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>https://beritajatim.com/ada-42-izin-jual-minol-diterbitkan-pemkot-malang-pks-minta-setop</t>
+          <t>https://timexkupang.fajar.co.id/2026/09/22/bais-tni-dan-aparat-gabungan-gagalkan-upaya-penyelundupan-miras-di-plbn-motaain/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>beritajatim.com</t>
+          <t>Timex Kupang</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -3561,26 +3561,26 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46287.29403935185</v>
+        <v>46287.49722222222</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BAIS TNI dan Aparat Gabungan Gagalkan Upaya Penyelundupan Miras di PLBN Mota’ain</t>
+          <t>Bupati Purbalingga Dukung Empat Raperda Prakarsa DPRD</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>https://timexkupang.fajar.co.id/2026/09/22/bais-tni-dan-aparat-gabungan-gagalkan-upaya-penyelundupan-miras-di-plbn-motaain/</t>
+          <t>https://rri.co.id/purwokerto/regional/2750221/bupati-purbalingga-dukung-empat-raperda-prakarsa-dprd</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Timex Kupang</t>
+          <t>rri.co.id</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3608,26 +3608,26 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46287.49722222222</v>
+        <v>46287.39778935185</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bupati Purbalingga Dukung Empat Raperda Prakarsa DPRD</t>
+          <t>Satgas Citarum Gagalkan Upaya Penyelundupan Minuman Beralkohol di PLBN Motaain</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/purwokerto/regional/2750221/bupati-purbalingga-dukung-empat-raperda-prakarsa-dprd</t>
+          <t>https://kupang.tribunnews.com/regional-ntt/980627/satgas-citarum-gagalkan-upaya-penyelundupan-minuman-beralkohol-di-plbn-motaain</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>rri.co.id</t>
+          <t>Pos-kupang.com</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -3655,26 +3655,26 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46287.39778935185</v>
+        <v>46287.19579861111</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Satgas Citarum Gagalkan Upaya Penyelundupan Minuman Beralkohol di PLBN Motaain</t>
+          <t>Soroti Penertiban Outlet Miras, Komisi A DPRD Madiun Akan Panggil Satpol PP</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>https://kupang.tribunnews.com/regional-ntt/980627/satgas-citarum-gagalkan-upaya-penyelundupan-minuman-beralkohol-di-plbn-motaain</t>
+          <t>https://beritajatim.com/soroti-penertiban-outlet-miras-komisi-a-dprd-madiun-akan-panggil-satpol-pp</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Pos-kupang.com</t>
+          <t>beritajatim.com</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -3702,21 +3702,21 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46287.19579861111</v>
+        <v>46287.35349537037</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Soroti Penertiban Outlet Miras, Komisi A DPRD Madiun Akan Panggil Satpol PP</t>
+          <t>Polisi Telusuri Dugaan Pungutan Liar ke Pengunjung RPTRA Kalijodo</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>https://beritajatim.com/soroti-penertiban-outlet-miras-komisi-a-dprd-madiun-akan-panggil-satpol-pp</t>
+          <t>https://www.cnnindonesia.com/nasional/20260922145804-12-1406866/polisi-telusuri-dugaan-pungutan-liar-ke-pengunjung-rptra-kalijodo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>beritajatim.com</t>
+          <t>CNN Indonesia</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3749,21 +3749,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46287.35349537037</v>
+        <v>46287.36666666667</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Polisi Telusuri Dugaan Pungutan Liar ke Pengunjung RPTRA Kalijodo</t>
+          <t>Polisi Telusuri Dugaan Pungli di Kawasan Kalijodo Jakarta</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnnindonesia.com/nasional/20260922145804-12-1406866/polisi-telusuri-dugaan-pungutan-liar-ke-pengunjung-rptra-kalijodo</t>
+          <t>https://rri.co.id/jakarta/hukum/kriminalitas/2749364/polisi-telusuri-dugaan-pungli-di-kawasan-kalijodo-jakarta</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CNN Indonesia</t>
+          <t>rri.co.id</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3796,26 +3796,26 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46287.36666666667</v>
+        <v>46287.20901620371</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Polisi Telusuri Dugaan Pungli di Kawasan Kalijodo Jakarta</t>
+          <t>Heboh Pool Party di Sukabumi Berujung Diprotes Warga, Panitia Minta Maaf</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/jakarta/hukum/kriminalitas/2749364/polisi-telusuri-dugaan-pungli-di-kawasan-kalijodo-jakarta</t>
+          <t>https://www.detik.com/jabar/berita/d-8673513/heboh-pool-party-di-sukabumi-berujung-diprotes-warga-panitia-minta-maaf</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>rri.co.id</t>
+          <t>detikcom</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -3843,26 +3843,26 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46287.20901620371</v>
+        <v>46287.17152777778</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Heboh Pool Party di Sukabumi Berujung Diprotes Warga, Panitia Minta Maaf</t>
+          <t>Radjoetasa, Bawa Arak Tradisional Bali, IWAK, Mendunia - harian.disway.id</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>https://www.detik.com/jabar/berita/d-8673513/heboh-pool-party-di-sukabumi-berujung-diprotes-warga-panitia-minta-maaf</t>
+          <t>https://harian.disway.id/read/969743/radjoetasa-bawa-arak-tradisional-bali-iwak-mendunia</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>detikcom</t>
+          <t>HARIAN DISWAY</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -3890,21 +3890,21 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46287.17152777778</v>
+        <v>46287.11699074074</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Radjoetasa, Bawa Arak Tradisional Bali, IWAK, Mendunia - harian.disway.id</t>
+          <t>BPOM Bakal Perketat Pengawasan Pemasaran Rokok Elektronik</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>https://harian.disway.id/read/969743/radjoetasa-bawa-arak-tradisional-bali-iwak-mendunia</t>
+          <t>https://ekonomi.bisnis.com/read/20260922/12/2006057/bpom-bakal-perketat-pengawasan-pemasaran-rokok-elektronik</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HARIAN DISWAY</t>
+          <t>Bisnis.com - Ekonomi</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>minuman beralkohol</t>
+          <t>nikotin</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3937,26 +3937,26 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46287.11699074074</v>
+        <v>46287.30054398148</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BPOM Bakal Perketat Pengawasan Pemasaran Rokok Elektronik</t>
+          <t>Teh Hijau, Bawa Tulus Borong Nominasi AMI Awards 2026</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>https://ekonomi.bisnis.com/read/20260922/12/2006057/bpom-bakal-perketat-pengawasan-pemasaran-rokok-elektronik</t>
+          <t>https://www.medcom.id/video/medcom-hiburan/PNg1oW8k-teh-hijau-bawa-tulus-borong-nominasi-ami-awards-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Bisnis.com - Ekonomi</t>
+          <t>Medcom.id</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>nikotin</t>
+          <t>teh</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -3984,26 +3984,26 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46287.30054398148</v>
+        <v>46287.66969907407</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Teh Hijau, Bawa Tulus Borong Nominasi AMI Awards 2026</t>
+          <t>Mesin Pembuat Susu Kedelai Beneran Praktis? Ini Review Produknya</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>https://www.medcom.id/video/medcom-hiburan/PNg1oW8k-teh-hijau-bawa-tulus-borong-nominasi-ami-awards-2026</t>
+          <t>https://rekomendit.detik.com/home-living/4801/mesin-pembuat-susu-kedelai-beneran-praktis-ini-review-produknya</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Medcom.id</t>
+          <t>Rekomendit</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>teh</t>
+          <t>susu</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4031,21 +4031,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46287.66969907407</v>
+        <v>46287.94930555556</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mesin Pembuat Susu Kedelai Beneran Praktis? Ini Review Produknya</t>
+          <t>Khofifah Unggulkan Sapi Perah Jatim yang Hasilkan 30 Liter Susu Sehari</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>https://rekomendit.detik.com/home-living/4801/mesin-pembuat-susu-kedelai-beneran-praktis-ini-review-produknya</t>
+          <t>https://surabaya.kompas.com/read/2026/09/23/054737978/khofifah-unggulkan-sapi-perah-jatim-yang-hasilkan-30-liter-susu-sehari</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Rekomendit</t>
+          <t>Kompas.com</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4078,21 +4078,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46287.94930555556</v>
+        <v>46287.13194444445</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Khofifah Unggulkan Sapi Perah Jatim yang Hasilkan 30 Liter Susu Sehari</t>
+          <t>Pencinta Kopi Wajib Tahu, Ada Banyak Susu Nabati Selain Oat Milk</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>https://surabaya.kompas.com/read/2026/09/23/054737978/khofifah-unggulkan-sapi-perah-jatim-yang-hasilkan-30-liter-susu-sehari</t>
+          <t>https://rri.co.id/samarinda/kuliner/2748670/pencinta-kopi-wajib-tahu-ada-banyak-susu-nabati-selain-oat-milk</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Kompas.com</t>
+          <t>rri.co.id</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4125,16 +4125,16 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46287.13194444445</v>
+        <v>46287.41944444444</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pencinta Kopi Wajib Tahu, Ada Banyak Susu Nabati Selain Oat Milk</t>
+          <t>Cara Menyimpan Buah Sawo Susu agar Tetap Berkualitas</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/samarinda/kuliner/2748670/pencinta-kopi-wajib-tahu-ada-banyak-susu-nabati-selain-oat-milk</t>
+          <t>https://rri.co.id/semarang/kuliner/2745343/cara-menyimpan-buah-sawo-susu-agar-tetap-berkualitas</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -4172,26 +4172,26 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46287.41944444444</v>
+        <v>46287.43958333333</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cara Menyimpan Buah Sawo Susu agar Tetap Berkualitas</t>
+          <t>8 Meme Anime tentang Sereal, Pakai Susu biar Lebih Enak?</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/semarang/kuliner/2745343/cara-menyimpan-buah-sawo-susu-agar-tetap-berkualitas</t>
+          <t>https://www.idntimes.com/hype/humor/meme-anime-tentang-sereal-c1c2-01-kn1ff-cl8j5x</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>rri.co.id</t>
+          <t>IDN Times</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -4219,26 +4219,26 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46287.43958333333</v>
+        <v>46287.85967592592</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8 Meme Anime tentang Sereal, Pakai Susu biar Lebih Enak?</t>
+          <t>Taru Martani Bantah Tak Terapkan SUSU, Ini Hasil Pemeriksaan Disnakertrans DIY</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>https://www.idntimes.com/hype/humor/meme-anime-tentang-sereal-c1c2-01-kn1ff-cl8j5x</t>
+          <t>https://jogjapolitan.harianjogja.com/r-1272298/taru-martani-bantah-tak-terapkan-susu-ini-hasil-pemeriksaan-disnakertrans-diy</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>IDN Times</t>
+          <t>Harian Jogja</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -4266,26 +4266,26 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46287.85967592592</v>
+        <v>46287.6280787037</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Taru Martani Bantah Tak Terapkan SUSU, Ini Hasil Pemeriksaan Disnakertrans DIY</t>
+          <t>Kapolres Pelabuhan Makassar Sapa Anak Pulau, Bagikan Susu, Snack dan Alat Tulis</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>https://jogjapolitan.harianjogja.com/r-1272298/taru-martani-bantah-tak-terapkan-susu-ini-hasil-pemeriksaan-disnakertrans-diy</t>
+          <t>https://rakyatsulsel.fajar.co.id/2026/09/22/kapolres-pelabuhan-makassar-sapa-anak-pulau-bagikan-susu-snack-dan-alat-tulis/</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Harian Jogja</t>
+          <t>Rakyat Sulsel</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -4313,21 +4313,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46287.6280787037</v>
+        <v>46287.53652777777</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kapolres Pelabuhan Makassar Sapa Anak Pulau, Bagikan Susu, Snack dan Alat Tulis</t>
+          <t>Kelola 130 Sapi Perah UPT Batu Hasilkan 600 Liter Susu per Hari, Sumbang PAD Jatim Rp1 M per Tahun</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>https://rakyatsulsel.fajar.co.id/2026/09/22/kapolres-pelabuhan-makassar-sapa-anak-pulau-bagikan-susu-snack-dan-alat-tulis/</t>
+          <t>https://surabaya.tribunnews.com/news/1950293/kelola-130-sapi-perah-upt-batu-hasilkan-600-liter-susu-per-hari-sumbang-pad-jatim-rp1-m-per-tahun</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Rakyat Sulsel</t>
+          <t>Surya.co.id</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4360,21 +4360,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46287.53652777777</v>
+        <v>46287.60101851852</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kelola 130 Sapi Perah UPT Batu Hasilkan 600 Liter Susu per Hari, Sumbang PAD Jatim Rp1 M per Tahun</t>
+          <t>Kelola 130 Sapi Perah, UPT Kota Batu Produksi 600 Liter Susu Sehari, Sumbang PAD Rp 1 Miliar / Tahun</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>https://surabaya.tribunnews.com/news/1950293/kelola-130-sapi-perah-upt-batu-hasilkan-600-liter-susu-per-hari-sumbang-pad-jatim-rp1-m-per-tahun</t>
+          <t>https://suryamalang.tribunnews.com/batu/288603/kelola-130-sapi-perah-upt-kota-batu-produksi-600-liter-susu-sehari-sumbang-pad-rp-1-miliar-tahun</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Surya.co.id</t>
+          <t>Suryamalang.com</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4407,26 +4407,26 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46287.60101851852</v>
+        <v>46287.61319444444</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kelola 130 Sapi Perah, UPT Kota Batu Produksi 600 Liter Susu Sehari, Sumbang PAD Rp 1 Miliar / Tahun</t>
+          <t>Seni dan Momen Terbaik Meracik Secangkir Kopi Susu Sempurna Penghilang Lelah - palpres.disway.id</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>https://suryamalang.tribunnews.com/batu/288603/kelola-130-sapi-perah-upt-kota-batu-produksi-600-liter-susu-sehari-sumbang-pad-rp-1-miliar-tahun</t>
+          <t>https://palpres.disway.id/lain-lain/read/779802/seni-dan-momen-terbaik-meracik-secangkir-kopi-susu-sempurna-penghilang-lelah</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Suryamalang.com</t>
+          <t>PALPRES.COM</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>susu</t>
+          <t>susu, kopi</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4454,21 +4454,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46287.61319444444</v>
+        <v>46287.03570601852</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Seni dan Momen Terbaik Meracik Secangkir Kopi Susu Sempurna Penghilang Lelah - palpres.disway.id</t>
+          <t>Senyum Anak Pulau, Kapolres Pelabuhan Makassar Bagikan Snack, Susu, dan Alat Tulis</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>https://palpres.disway.id/lain-lain/read/779802/seni-dan-momen-terbaik-meracik-secangkir-kopi-susu-sempurna-penghilang-lelah</t>
+          <t>https://harian.fajar.co.id/2026/09/22/senyum-anak-pulau-kapolres-pelabuhan-makassar-bagikan-snack-susu-dan-alat-tulis/</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PALPRES.COM</t>
+          <t>harian fajar</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>susu, kopi</t>
+          <t>susu</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4501,21 +4501,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46287.03570601852</v>
+        <v>46287.96528935185</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Senyum Anak Pulau, Kapolres Pelabuhan Makassar Bagikan Snack, Susu, dan Alat Tulis</t>
+          <t>Keputihan bening seperti susu ada bercak darah sedikit apakah hamil</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>https://harian.fajar.co.id/2026/09/22/senyum-anak-pulau-kapolres-pelabuhan-makassar-bagikan-snack-susu-dan-alat-tulis/</t>
+          <t>https://hellosehat.com/community/kesehatan-wanita/keputihan-bening-seperti-susu-ada-bercak-darah-sedikit-apakah-hamil-269188/</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>harian fajar</t>
+          <t>Hello Sehat</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4548,21 +4548,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46287.96528935185</v>
+        <v>46287.48104166667</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Keputihan bening seperti susu ada bercak darah sedikit apakah hamil</t>
+          <t>Jam Pulang Sekolah, Polisi Hadir di Persimpangan MIN 9 Langkat</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>https://hellosehat.com/community/kesehatan-wanita/keputihan-bening-seperti-susu-ada-bercak-darah-sedikit-apakah-hamil-269188/</t>
+          <t>https://tribratanews.reslangkat.sumut.polri.go.id/jam-pulang-sekolah-polisi-hadir-di-persimpangan-min-9-langkat/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Hello Sehat</t>
+          <t>Website Resmi Polri</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4595,26 +4595,26 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46287.48104166667</v>
+        <v>46287.14797453704</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jam Pulang Sekolah, Polisi Hadir di Persimpangan MIN 9 Langkat</t>
+          <t>Waktunya membangun industri air mineral laut dalam</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>https://tribratanews.reslangkat.sumut.polri.go.id/jam-pulang-sekolah-polisi-hadir-di-persimpangan-min-9-langkat/</t>
+          <t>https://megapolitan.antaranews.com/berita/551128/waktunya-membangun-industri-air-mineral-laut-dalam</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Website Resmi Polri</t>
+          <t>ANTARA News Megapolitan</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>susu</t>
+          <t>air minum dalam kemasan</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -4642,21 +4642,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46287.14797453704</v>
+        <v>46287.20625</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Waktunya membangun industri air mineral laut dalam</t>
+          <t>PDAM Bondowoso Diduga Mark Up Harga Gelas Air Minum dalam Kemasan</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>https://megapolitan.antaranews.com/berita/551128/waktunya-membangun-industri-air-mineral-laut-dalam</t>
+          <t>https://timesindonesia.co.id/read/news/609633/pdam-bondowoso-diduga-mark-up-harga-gelas-air-minum-dalam-kemasan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ANTARA News Megapolitan</t>
+          <t>TIMES Indonesia</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4689,26 +4689,26 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46287.20625</v>
+        <v>46287.46053240741</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PDAM Bondowoso Diduga Mark Up Harga Gelas Air Minum dalam Kemasan</t>
+          <t>Personil Polsek Ngraho Laksanakan Patroli dialogis Siang Hari di Warung kopi untuk Antisipasi Tindak Kejahatan 3C</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>https://timesindonesia.co.id/read/news/609633/pdam-bondowoso-diduga-mark-up-harga-gelas-air-minum-dalam-kemasan</t>
+          <t>https://tribratanews.resbojonegoro.jatim.polri.go.id/personil-polsek-ngraho-laksanakan-patroli-dialogis-siang-hari-di-warung-kopi-untuk-antisipasi-tindak-kejahatan-3c-4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TIMES Indonesia</t>
+          <t>Tribratanews Polres Bojonegoro</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>air minum dalam kemasan</t>
+          <t>kopi</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4736,26 +4736,26 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46287.46053240741</v>
+        <v>46287.55208333334</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Personil Polsek Ngraho Laksanakan Patroli dialogis Siang Hari di Warung kopi untuk Antisipasi Tindak Kejahatan 3C</t>
+          <t>Kopi dan Teh Terlalu Panas Bisa Picu Risiko Kanker Kerongkongan, Ini Hasil Penelitiannya - Suara Merdeka</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>https://tribratanews.resbojonegoro.jatim.polri.go.id/personil-polsek-ngraho-laksanakan-patroli-dialogis-siang-hari-di-warung-kopi-untuk-antisipasi-tindak-kejahatan-3c-4</t>
+          <t>https://www.suaramerdeka.com/gaya-hidup/0417666253/kopi-dan-teh-terlalu-panas-bisa-picu-risiko-kanker-kerongkongan-ini-hasil-penelitiannya</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tribratanews Polres Bojonegoro</t>
+          <t>suaramerdeka.com</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -4783,26 +4783,26 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46287.55208333334</v>
+        <v>46287.6844212963</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kopi dan Teh Terlalu Panas Bisa Picu Risiko Kanker Kerongkongan, Ini Hasil Penelitiannya - Suara Merdeka</t>
+          <t>Kopdes Mulai Ekspor, Kopi dan Arang Tembus Mesir-Tiongkok</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>https://www.suaramerdeka.com/gaya-hidup/0417666253/kopi-dan-teh-terlalu-panas-bisa-picu-risiko-kanker-kerongkongan-ini-hasil-penelitiannya</t>
+          <t>https://www.metrotvnews.com/read/b3JC54p7-kopdes-mulai-ekspor-kopi-dan-arang-tembus-mesir-tiongkok</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>suaramerdeka.com</t>
+          <t>metrotvnews.com</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -4830,26 +4830,26 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46287.6844212963</v>
+        <v>46287.35696759259</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kopdes Mulai Ekspor, Kopi dan Arang Tembus Mesir-Tiongkok</t>
+          <t>Garap ”GI Tourism” Dieng lewat Carica, Kopi, dan Purwaceng</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrotvnews.com/read/b3JC54p7-kopdes-mulai-ekspor-kopi-dan-arang-tembus-mesir-tiongkok</t>
+          <t>https://www.kompas.id/artikel/garap-gi-tourism-dieng-lewat-carica-kopi-dan-purwaceng?open_from=Nasional_Page</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>metrotvnews.com</t>
+          <t>Kompas.id</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -4877,16 +4877,16 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46287.35696759259</v>
+        <v>46287.38824074074</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Garap ”GI Tourism” Dieng lewat Carica, Kopi, dan Purwaceng</t>
+          <t>Mengunjungi Kebun Kopi di Jakarta</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompas.id/artikel/garap-gi-tourism-dieng-lewat-carica-kopi-dan-purwaceng?open_from=Nasional_Page</t>
+          <t>https://www.kompas.id/artikel/merawat-harapan-pada-setangkai-pohon-kopi?open_from=Nasional_Page</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4924,21 +4924,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46287.38824074074</v>
+        <v>46287.60541666667</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mengunjungi Kebun Kopi di Jakarta</t>
+          <t>Sleman meluncurkan Kopi Keliling Merapi perkuat pemasaran kopi lokal</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompas.id/artikel/merawat-harapan-pada-setangkai-pohon-kopi?open_from=Nasional_Page</t>
+          <t>https://jogja.antaranews.com/berita/855548/sleman-meluncurkan-kopi-keliling-merapi-perkuat-pemasaran-kopi-lokal</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Kompas.id</t>
+          <t>ANTARA News Yogyakarta</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4971,26 +4971,26 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46287.60541666667</v>
+        <v>46287.31284722222</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sleman meluncurkan Kopi Keliling Merapi perkuat pemasaran kopi lokal</t>
+          <t>FOTO: Menelusuri Kebun Kopi di Pinggiran Jakarta</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>https://jogja.antaranews.com/berita/855548/sleman-meluncurkan-kopi-keliling-merapi-perkuat-pemasaran-kopi-lokal</t>
+          <t>https://www.cnnindonesia.com/gaya-hidup/20260922124955-286-1406746/foto-menelusuri-kebun-kopi-di-pinggiran-jakarta</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ANTARA News Yogyakarta</t>
+          <t>cnnindonesia.com</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -5018,26 +5018,26 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46287.31284722222</v>
+        <v>46287.50584490741</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FOTO: Menelusuri Kebun Kopi di Pinggiran Jakarta</t>
+          <t>Honda DBL with Kopi Good Day 2026 East Java-East Resmi Bergulir, Jember Jadi Panggung Adu Gengsi Basket Pelajar</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnnindonesia.com/gaya-hidup/20260922124955-286-1406746/foto-menelusuri-kebun-kopi-di-pinggiran-jakarta</t>
+          <t>https://ppid.jemberkab.go.id/berita/honda-dbl-with-kopi-good-day-2026-east-java-east-resmi-bergulir-jember-jadi-panggung-adu-gengsi-basket-pelajar-20260922</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>cnnindonesia.com</t>
+          <t>PPID Kabupaten Jember</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -5065,26 +5065,26 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46287.50584490741</v>
+        <v>46287.89444444444</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Honda DBL with Kopi Good Day 2026 East Java-East Resmi Bergulir, Jember Jadi Panggung Adu Gengsi Basket Pelajar</t>
+          <t>Sejarah Singkat Kopi Java Buana Ciremai</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>https://ppid.jemberkab.go.id/berita/honda-dbl-with-kopi-good-day-2026-east-java-east-resmi-bergulir-jember-jadi-panggung-adu-gengsi-basket-pelajar-20260922</t>
+          <t>https://rri.co.id/bandung/berita-lain/2751203/sejarah-singkat-kopi-java-buana-ciremai</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PPID Kabupaten Jember</t>
+          <t>RRI.co.id</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -5112,16 +5112,16 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46287.89444444444</v>
+        <v>46287.49791666667</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sejarah Singkat Kopi Java Buana Ciremai</t>
+          <t>Kopi Dieng Tembus 3 Negara, Wisata Berbasis Indikasi Geografis Disiapkan</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/bandung/berita-lain/2751203/sejarah-singkat-kopi-java-buana-ciremai</t>
+          <t>https://rri.co.id/purwokerto/regional/2749662/kopi-dieng-tembus-3-negara-wisata-berbasis-indikasi-geografis-disiapkan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -5159,21 +5159,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46287.49791666667</v>
+        <v>46287.17638888889</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kopi Dieng Tembus 3 Negara, Wisata Berbasis Indikasi Geografis Disiapkan</t>
+          <t>Pembukaan Festival Kopi Kerinci, Saatnya Kopi Lokal Naik Kelas dan Unjuk Kualitas - jektvnews.disway.id</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/purwokerto/regional/2749662/kopi-dieng-tembus-3-negara-wisata-berbasis-indikasi-geografis-disiapkan</t>
+          <t>https://jektvnews.disway.id/berita/read/26845/pembukaan-festival-kopi-kerinci-saatnya-kopi-lokal-naik-kelas-dan-unjuk-kualitas</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RRI.co.id</t>
+          <t>Disway</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5206,16 +5206,16 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46287.17638888889</v>
+        <v>46287.58611111111</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pembukaan Festival Kopi Kerinci, Saatnya Kopi Lokal Naik Kelas dan Unjuk Kualitas - jektvnews.disway.id</t>
+          <t>Kopi Moe Simpang Pulai Jambi Tempat Nongkrong Nyaman untuk Keluarga dan Pekerja Kantor - jektvnews.disway.id</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>https://jektvnews.disway.id/berita/read/26845/pembukaan-festival-kopi-kerinci-saatnya-kopi-lokal-naik-kelas-dan-unjuk-kualitas</t>
+          <t>https://jektvnews.disway.id/adv/read/26866/kopi-moe-simpang-pulai-jambi-tempat-nongkrong-nyaman-untuk-keluarga-dan-pekerja-kantor</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -5253,26 +5253,26 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46287.58611111111</v>
+        <v>46287.51527777778</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kopi Moe Simpang Pulai Jambi Tempat Nongkrong Nyaman untuk Keluarga dan Pekerja Kantor - jektvnews.disway.id</t>
+          <t>Kenalkan Kopi Nirmalagiri, Koling dan Darling Mangkal di Kawasan Wisata Merapi</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>https://jektvnews.disway.id/adv/read/26866/kopi-moe-simpang-pulai-jambi-tempat-nongkrong-nyaman-untuk-keluarga-dan-pekerja-kantor</t>
+          <t>https://rri.co.id/yogyakarta/regional/2750714/kenalkan-kopi-nirmalagiri-koling-dan-darling-mangkal-di-kawasan-wisata-merapi</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Disway</t>
+          <t>RRI.co.id</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -5300,21 +5300,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46287.51527777778</v>
+        <v>46287.17569444444</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kenalkan Kopi Nirmalagiri, Koling dan Darling Mangkal di Kawasan Wisata Merapi</t>
+          <t>Festival Kopi Kerinci 2026 Siap Digelar, Angkat Kopi Lokal Menuju Panggung Dunia - jektvnews.disway.id</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/yogyakarta/regional/2750714/kenalkan-kopi-nirmalagiri-koling-dan-darling-mangkal-di-kawasan-wisata-merapi</t>
+          <t>https://jektvnews.disway.id/berita/read/26844/festival-kopi-kerinci-2026-siap-digelar-angkat-kopi-lokal-menuju-panggung-dunia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>RRI.co.id</t>
+          <t>Disway</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5347,21 +5347,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46287.17569444444</v>
+        <v>46287.62293981481</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Festival Kopi Kerinci 2026 Siap Digelar, Angkat Kopi Lokal Menuju Panggung Dunia - jektvnews.disway.id</t>
+          <t>Kopi Keliling dan Darling Merapi Siap Jangkau Titik Keramaian dan Wisata di Sleman</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>https://jektvnews.disway.id/berita/read/26844/festival-kopi-kerinci-2026-siap-digelar-angkat-kopi-lokal-menuju-panggung-dunia</t>
+          <t>https://jogjapolitan.harianjogja.com/r-1272263/kopi-keliling-dan-darling-merapi-siap-jangkau-titik-keramaian-dan-wisata-di-sleman</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Disway</t>
+          <t>Harian Jogja</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5394,26 +5394,26 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46287.62293981481</v>
+        <v>46287.14513888889</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kopi Keliling dan Darling Merapi Siap Jangkau Titik Keramaian dan Wisata di Sleman</t>
+          <t>Benarkah Sering Minum Kopi Picu Batu Ginjal? Dokter Ungkap Faktanya</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>https://jogjapolitan.harianjogja.com/r-1272263/kopi-keliling-dan-darling-merapi-siap-jangkau-titik-keramaian-dan-wisata-di-sleman</t>
+          <t>https://health.tribunnews.com/penyakit-umum/42528/benarkah-sering-minum-kopi-picu-batu-ginjal-dokter-ungkap-faktanya</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Harian Jogja</t>
+          <t>Tribunnews.com</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -5441,26 +5441,26 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46287.14513888889</v>
+        <v>46287.17194444445</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Benarkah Sering Minum Kopi Picu Batu Ginjal? Dokter Ungkap Faktanya</t>
+          <t>Arabika Gayo Indonesia Masuk sebagai Biji Kopi Terbaik di Dunia 2026</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>https://health.tribunnews.com/penyakit-umum/42528/benarkah-sering-minum-kopi-picu-batu-ginjal-dokter-ungkap-faktanya</t>
+          <t>https://www.idntimes.com/food/diet/biji-kopi-terbaik-di-dunia-2026-00-z5hk4-b7cdrj</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tribunnews.com</t>
+          <t>IDN Times</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -5488,26 +5488,26 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46287.17194444445</v>
+        <v>46287.50913194445</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Arabika Gayo Indonesia Masuk sebagai Biji Kopi Terbaik di Dunia 2026</t>
+          <t>Tiga Tahun Menanti, Balpus Akhirnya Tampil di Honda DBL with Kopi Good Day 2026 East Jakarta</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>https://www.idntimes.com/food/diet/biji-kopi-terbaik-di-dunia-2026-00-z5hk4-b7cdrj</t>
+          <t>https://wartakota.tribunnews.com/sport/902141/tiga-tahun-menanti-balpus-akhirnya-tampil-di-honda-dbl-with-kopi-good-day-2026-east-jakarta</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>IDN Times</t>
+          <t>Wartakotalive.com</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -5535,21 +5535,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46287.50913194445</v>
+        <v>46287.55138888889</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tiga Tahun Menanti, Balpus Akhirnya Tampil di Honda DBL with Kopi Good Day 2026 East Jakarta</t>
+          <t>Kopi Nusantara Tak Lagi Sekadar Minuman, Kini Jadi Pengalaman Premium</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>https://wartakota.tribunnews.com/sport/902141/tiga-tahun-menanti-balpus-akhirnya-tampil-di-honda-dbl-with-kopi-good-day-2026-east-jakarta</t>
+          <t>https://www.inews.id/travel/kuliner/kopi-nusantara-tak-lagi-sekadar-minuman-kini-jadi-pengalaman-premium</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wartakotalive.com</t>
+          <t>iNews.ID</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5582,26 +5582,26 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46287.55138888889</v>
+        <v>46287.96388888889</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kopi Nusantara Tak Lagi Sekadar Minuman, Kini Jadi Pengalaman Premium</t>
+          <t>Kopi Sungai Bermas Kian Menggeliat, UMKM Lokal Kerinci Tembus Pasar Harian - https://jambiekspres.disway.id/</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>https://www.inews.id/travel/kuliner/kopi-nusantara-tak-lagi-sekadar-minuman-kini-jadi-pengalaman-premium</t>
+          <t>https://jambiekspres.disway.id/ekonomi/read/723065/kopi-sungai-bermas-kian-menggeliat-umkm-lokal-kerinci-tembus-pasar-harian</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>iNews.ID</t>
+          <t>Jambi Ekspres</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -5629,26 +5629,26 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46287.96388888889</v>
+        <v>46287.58511574074</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kopi Sungai Bermas Kian Menggeliat, UMKM Lokal Kerinci Tembus Pasar Harian - https://jambiekspres.disway.id/</t>
+          <t>Pergeseran Paradigma Kopi Indonesia di Australia Halaman 1</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>https://jambiekspres.disway.id/ekonomi/read/723065/kopi-sungai-bermas-kian-menggeliat-umkm-lokal-kerinci-tembus-pasar-harian</t>
+          <t>https://www.kompasiana.com/merzagamal8924/6ab2893ced64153473408323/pergeseran-paradigma-kopi-indonesia-di-australia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Jambi Ekspres</t>
+          <t>kompasiana.com</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -5676,26 +5676,26 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46287.58511574074</v>
+        <v>46287.5975</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Pergeseran Paradigma Kopi Indonesia di Australia Halaman 1</t>
+          <t>Uji Jalur GI Tourism, Kopi Arabika Pegunungan Dieng Didorong Jadi Pengalaman Wisata Edukatif</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompasiana.com/merzagamal8924/6ab2893ced64153473408323/pergeseran-paradigma-kopi-indonesia-di-australia</t>
+          <t>https://jateng.tribunnews.com/kilas/1267205/uji-jalur-gi-tourism-kopi-arabika-pegunungan-dieng-didorong-jadi-pengalaman-wisata-edukatif</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>kompasiana.com</t>
+          <t>Tribunjateng.com</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -5723,21 +5723,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46287.5975</v>
+        <v>46287.78571759259</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Uji Jalur GI Tourism, Kopi Arabika Pegunungan Dieng Didorong Jadi Pengalaman Wisata Edukatif</t>
+          <t>Lebih dari Secangkir Kopi, Manglayang Bliss Bawa Cerita Petani Lokal dan Halaman 1</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>https://jateng.tribunnews.com/kilas/1267205/uji-jalur-gi-tourism-kopi-arabika-pegunungan-dieng-didorong-jadi-pengalaman-wisata-edukatif</t>
+          <t>https://www.kompasiana.com/kamilaavia4268/6ab2ce2eed64155f317580ee/lebih-dari-secangkir-kopi-manglayang-bliss-bawa-cerita-petani-lokal-dan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tribunjateng.com</t>
+          <t>kompasiana.com</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5770,21 +5770,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46287.78571759259</v>
+        <v>46287.44400462963</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lebih dari Secangkir Kopi, Manglayang Bliss Bawa Cerita Petani Lokal dan Halaman 1</t>
+          <t>Kopi Turajaji, Warisan 600 Tahun dari Ende yang Kini Menembus Pasar Dunia</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompasiana.com/kamilaavia4268/6ab2ce2eed64155f317580ee/lebih-dari-secangkir-kopi-manglayang-bliss-bawa-cerita-petani-lokal-dan</t>
+          <t>https://flores.tribunnews.com/ende/65407/kopi-turajaji-warisan-600-tahun-dari-ende-yang-kini-menembus-pasar-dunia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>kompasiana.com</t>
+          <t>Tribunflores.com</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5817,26 +5817,26 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46287.44400462963</v>
+        <v>46287.58788194445</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kopi Turajaji, Warisan 600 Tahun dari Ende yang Kini Menembus Pasar Dunia</t>
+          <t>Kopi Oleh-Oleh Khas Nusantara, Cita Rasa Autentik dalam Setiap Cangkir</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>https://flores.tribunnews.com/ende/65407/kopi-turajaji-warisan-600-tahun-dari-ende-yang-kini-menembus-pasar-dunia</t>
+          <t>https://www.jpnn.com/news/kopi-oleh-oleh-khas-nusantara-cita-rasa-autentik-dalam-setiap-cangkir</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Tribunflores.com</t>
+          <t>JPNN.com</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -5864,26 +5864,26 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46287.58788194445</v>
+        <v>46287.5555787037</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kopi Oleh-Oleh Khas Nusantara, Cita Rasa Autentik dalam Setiap Cangkir</t>
+          <t>Harga Gelondongan Kopi di Gayo Lues Naik Tipis Hari Ini 22 September 2026</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>https://www.jpnn.com/news/kopi-oleh-oleh-khas-nusantara-cita-rasa-autentik-dalam-setiap-cangkir</t>
+          <t>https://gayo.tribunnews.com/gayo-lues/54318/harga-gelondongan-kopi-di-gayo-lues-naik-tipis-hari-ini-22-september-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>JPNN.com</t>
+          <t>tribungayo.com</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -5911,21 +5911,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46287.5555787037</v>
+        <v>46287.43850694445</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Harga Gelondongan Kopi di Gayo Lues Naik Tipis Hari Ini 22 September 2026</t>
+          <t>Sleman Perkuat Pemasaran Kopi Lokal Lewat Koling dan Darling Merapi</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>https://gayo.tribunnews.com/gayo-lues/54318/harga-gelondongan-kopi-di-gayo-lues-naik-tipis-hari-ini-22-september-2026</t>
+          <t>https://jogja.tribunnews.com/diy/1223705/sleman-perkuat-pemasaran-kopi-lokal-lewat-koling-dan-darling-merapi</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>tribungayo.com</t>
+          <t>Tribunjogja.com</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5958,21 +5958,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46287.43850694445</v>
+        <v>46287.54540509259</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sleman Perkuat Pemasaran Kopi Lokal Lewat Koling dan Darling Merapi</t>
+          <t>Kim Woo Bin Kirim Truk Kopi Manis untuk Dukungan Shin Min Ah di Lokasi Syuting</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>https://jogja.tribunnews.com/diy/1223705/sleman-perkuat-pemasaran-kopi-lokal-lewat-koling-dan-darling-merapi</t>
+          <t>https://www.wowkeren.com/berita/tampil/00536181.html</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tribunjogja.com</t>
+          <t>wowkeren.com</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6005,26 +6005,26 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46287.54540509259</v>
+        <v>46287.50085648148</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kim Woo Bin Kirim Truk Kopi Manis untuk Dukungan Shin Min Ah di Lokasi Syuting</t>
+          <t>Toko Kopi Bakeri di Padang</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>https://www.wowkeren.com/berita/tampil/00536181.html</t>
+          <t>https://www.pinterest.com/pin/843087992791170257/</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>wowkeren.com</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -6052,21 +6052,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46287.50085648148</v>
+        <v>46287.03177083333</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Toko Kopi Bakeri di Padang</t>
+          <t>13 Kopi Bubuk Terbaik yang Wajib Dicoba Pecinta Kopi</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>https://www.pinterest.com/pin/843087992791170257/</t>
+          <t>https://www.alodokter.com/kopi-bubuk-terbaik-yang-wajib-dicoba-pecinta-kopi</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Alodokter</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6099,26 +6099,26 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46287.03177083333</v>
+        <v>46287.58679398148</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>13 Kopi Bubuk Terbaik yang Wajib Dicoba Pecinta Kopi</t>
+          <t>Pemerintah Dorong Koperasi Petani Sawit Miliki Pabrik CPO Sendiri</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>https://www.alodokter.com/kopi-bubuk-terbaik-yang-wajib-dicoba-pecinta-kopi</t>
+          <t>https://www.metrotvnews.com/play/NQAC0Pq1-pemerintah-dorong-koperasi-petani-sawit-miliki-pabrik-cpo-sendiri</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Alodokter</t>
+          <t>metrotvnews.com</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>kopi</t>
+          <t>cpo, sawit</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -6146,26 +6146,26 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46287.58679398148</v>
+        <v>46287.14769675926</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Pemerintah Dorong Koperasi Petani Sawit Miliki Pabrik CPO Sendiri</t>
+          <t>Harga CPO Diproyeksi Tetap di Atas US$ 1,154 per Ton hingga Akhir 2026</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>https://www.metrotvnews.com/play/NQAC0Pq1-pemerintah-dorong-koperasi-petani-sawit-miliki-pabrik-cpo-sendiri</t>
+          <t>https://internasional.kontan.co.id/news/harga-cpo-diproyeksi-tetap-di-atas-us-1154-per-ton-hingga-akhir-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>metrotvnews.com</t>
+          <t>kontan.co.id</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>cpo, sawit</t>
+          <t>cpo, minyak sawit</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -6193,26 +6193,26 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46287.14769675926</v>
+        <v>46287.11927083333</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Harga CPO Diproyeksi Tetap di Atas US$ 1,154 per Ton hingga Akhir 2026</t>
+          <t>Bukan Cuma Jual TBS, Petani Sawit Didorong Punya Pabrik CPO Sendiri</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>https://internasional.kontan.co.id/news/harga-cpo-diproyeksi-tetap-di-atas-us-1154-per-ton-hingga-akhir-2026</t>
+          <t>https://www.suara.com/bisnis/2026/09/22/095145/bukan-cuma-jual-tbs-petani-sawit-didorong-punya-pabrik-cpo-sendiri</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>kontan.co.id</t>
+          <t>Suara.com</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>cpo, minyak sawit</t>
+          <t>cpo, sawit</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -6240,26 +6240,26 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46287.32013888889</v>
+        <v>46287.00972222222</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Turun, Harga Kelapa Sawit Mitra Plasma Minggu Ini Jadi Rp3.948 per Kg</t>
+          <t>Start-Up DCS TRKI Mengawal Transformasi Minyak Sawit Menjadi Cetyl Alcohol</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>https://mediacenter.riau.go.id/read/turun-harga-kelapa-sawit-mitra-plasma-minggu-ini-jadi-rp3948-per-kg</t>
+          <t>https://www.kompasiana.com/endyyulianto8437/6ab1c76134777c4955725b72/start-up-dcs-trki-mengawal-transformasi-minyak-sawit-menjadi-cetyl-alcohol</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Media Center Riau</t>
+          <t>kompasiana.com</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>cpo</t>
+          <t>cpo, minyak sawit, fame, sawit</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -6287,26 +6287,26 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46287.11927083333</v>
+        <v>46287.34722222222</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bukan Cuma Jual TBS, Petani Sawit Didorong Punya Pabrik CPO Sendiri</t>
+          <t>Harga CPO Global Lesu, Banderol Sawit Plasma Riau Sepekan ke Depan Turun Tipis</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>https://www.suara.com/bisnis/2026/09/22/095145/bukan-cuma-jual-tbs-petani-sawit-didorong-punya-pabrik-cpo-sendiri</t>
+          <t>https://www.goriau.com/ragam/harga-cpo-global-lesu-banderol-sawit-plasma-riau-sepekan-ke-depan-turun-tipis.html</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Suara.com</t>
+          <t>GoRiau.com</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -6334,26 +6334,26 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46287.00972222222</v>
+        <v>46287.35625</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Start-Up DCS TRKI Mengawal Transformasi Minyak Sawit Menjadi Cetyl Alcohol</t>
+          <t>Harga CPO Terkoreksi, Nilai Jual Sawit Swadaya Riau Turun ke Angka Rp3.885</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompasiana.com/endyyulianto8437/6ab1c76134777c4955725b72/start-up-dcs-trki-mengawal-transformasi-minyak-sawit-menjadi-cetyl-alcohol</t>
+          <t>https://www.goriau.com/ragam/harga-cpo-terkoreksi-nilai-jual-sawit-swadaya-riau-turun-ke-angka-rp3885.html</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>kompasiana.com</t>
+          <t>GoRiau.com</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>cpo, minyak sawit, fame, sawit</t>
+          <t>cpo, sawit</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -6381,21 +6381,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46287.34722222222</v>
+        <v>46287.30247685185</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Harga CPO Global Lesu, Banderol Sawit Plasma Riau Sepekan ke Depan Turun Tipis</t>
+          <t>Kasasi Ditolak, Advokat Ariyanto 'Gadun FM' Tetap Dihukum 16 Tahun Bui</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>https://www.goriau.com/ragam/harga-cpo-global-lesu-banderol-sawit-plasma-riau-sepekan-ke-depan-turun-tipis.html</t>
+          <t>https://www.cnnindonesia.com/nasional/20260922103520-12-1406664/kasasi-ditolak-advokat-ariyanto-gadun-fm-tetap-dihukum-16-tahun-bui</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GoRiau.com</t>
+          <t>cnnindonesia.com</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>cpo, sawit</t>
+          <t>cpo</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -6428,21 +6428,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46287.35625</v>
+        <v>46287.04162037037</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Harga CPO Terkoreksi, Nilai Jual Sawit Swadaya Riau Turun ke Angka Rp3.885</t>
+          <t>PalmCo Jamin Ketertelusuran Asal-Usul CPO untuk Penuhi Tuntutan Pasar Global</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>https://www.goriau.com/ragam/harga-cpo-terkoreksi-nilai-jual-sawit-swadaya-riau-turun-ke-angka-rp3885.html</t>
+          <t>https://haisawit.co.id/news/detail/palmco-jamin-ketertelusuran-asalusul-cpo-untuk-penuhi-tuntutan-pasar-global</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>GoRiau.com</t>
+          <t>HaiSawit</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6475,26 +6475,26 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46287.30247685185</v>
+        <v>46287.05206018518</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kasasi Ditolak, Advokat Ariyanto 'Gadun FM' Tetap Dihukum 16 Tahun Bui</t>
+          <t>PalmCo Catat Produksi CPO Lebih dari 1,2 Juta Ton pada Semester I-2026</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnnindonesia.com/nasional/20260922103520-12-1406664/kasasi-ditolak-advokat-ariyanto-gadun-fm-tetap-dihukum-16-tahun-bui</t>
+          <t>https://haisawit.co.id/news/detail/palmco-catat-produksi-cpo-lebih-dari-12-juta-ton-pada-semester-i2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>cnnindonesia.com</t>
+          <t>HaiSawit</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>cpo</t>
+          <t>cpo, sawit</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -6522,26 +6522,26 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46287.04162037037</v>
+        <v>46287.11009259259</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PalmCo Jamin Ketertelusuran Asal-Usul CPO untuk Penuhi Tuntutan Pasar Global</t>
+          <t>E50 dan Aspek Kunci yang Perlu Diperhatikan</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>https://haisawit.co.id/news/detail/palmco-jamin-ketertelusuran-asalusul-cpo-untuk-penuhi-tuntutan-pasar-global</t>
+          <t>https://www.cnbcindonesia.com/opini/20260922093139-14-769768/e50-dan-aspek-kunci-yang-perlu-diperhatikan</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>HaiSawit</t>
+          <t>CNBC Indonesia</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>cpo, sawit</t>
+          <t>cpo, biodiesel</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -6569,26 +6569,26 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46287.05206018518</v>
+        <v>46287.49686342593</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PalmCo Catat Produksi CPO Lebih dari 1,2 Juta Ton pada Semester I-2026</t>
+          <t>Gerak Saham Emiten Konglomerat Salim hingga Prajogo, Siapa Paling Cuan?</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>https://haisawit.co.id/news/detail/palmco-catat-produksi-cpo-lebih-dari-12-juta-ton-pada-semester-i2026</t>
+          <t>https://market.bisnis.com/read/20260922/189/2006284/gerak-saham-emiten-konglomerat-salim-hingga-prajogo-siapa-paling-cuan</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>HaiSawit</t>
+          <t>Bisnis.com - Market</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>cpo, sawit</t>
+          <t>cpo</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -6616,21 +6616,21 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46287.11009259259</v>
+        <v>46287.51388888889</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>E50 dan Aspek Kunci yang Perlu Diperhatikan</t>
+          <t>Harga CPO diproyeksi tembus US$1.154 hingga akhir 2026</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnbcindonesia.com/opini/20260922093139-14-769768/e50-dan-aspek-kunci-yang-perlu-diperhatikan</t>
+          <t>https://www.idnfinancials.com/id/news/69231/harga-cpo-diproyeksi-tembus-us1-154-hingga-akhir-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CNBC Indonesia</t>
+          <t>IDNFinancials</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>cpo, biodiesel</t>
+          <t>cpo</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -6663,26 +6663,26 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46287.49686342593</v>
+        <v>46287.17013888889</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Gerak Saham Emiten Konglomerat Salim hingga Prajogo, Siapa Paling Cuan?</t>
+          <t>Sidang Korupsi Ekspor CPO, Empat Saksi Ungkap Peta Hilirisasi dan HS Code</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>https://market.bisnis.com/read/20260922/189/2006284/gerak-saham-emiten-konglomerat-salim-hingga-prajogo-siapa-paling-cuan</t>
+          <t>https://seputarborneo.com/news/25942-sidang-korupsi-ekspor-cpo-empat-saksi-ungkap-peta-hilirisasi-dan-hs-code.html</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Bisnis.com - Market</t>
+          <t>Berita Seputar Borneo</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6710,26 +6710,26 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46287.51388888889</v>
+        <v>46287.18263888889</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Harga CPO diproyeksi tembus US$1.154 hingga akhir 2026</t>
+          <t>Empat Saksi Diperiksa dalam Sidang Korupsi Ekspor CPO</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>https://www.idnfinancials.com/id/news/69231/harga-cpo-diproyeksi-tembus-us1-154-hingga-akhir-2026</t>
+          <t>https://hukum.tvrinews.com/berita/t4in7b5-empat-saksi-diperiksa-dalam-sidang-korupsi-ekspor-cpo</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>IDNFinancials</t>
+          <t>TVRI News</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -6757,26 +6757,26 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46287.17013888889</v>
+        <v>46287.13888888889</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sidang Korupsi Ekspor CPO, Empat Saksi Ungkap Peta Hilirisasi dan HS Code</t>
+          <t>Kejar ketahanan energi, Indonesia konversi batu bara jadi BBM</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>https://seputarborneo.com/news/25942-sidang-korupsi-ekspor-cpo-empat-saksi-ungkap-peta-hilirisasi-dan-hs-code.html</t>
+          <t>https://www.idnfinancials.com/id/news/69208/kejar-ketahanan-energi-indonesia-konversi-batu-bara-jadi-bbm</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Berita Seputar Borneo</t>
+          <t>IDNFinancials</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -6788,12 +6788,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>cpo</t>
+          <t>minyak sawit</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -6804,26 +6804,26 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46287.18263888889</v>
+        <v>46287.42222222222</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Empat Saksi Diperiksa dalam Sidang Korupsi Ekspor CPO</t>
+          <t>Tantangan Implementasi Bahan Bakar Biodiesel B50</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>https://hukum.tvrinews.com/berita/t4in7b5-empat-saksi-diperiksa-dalam-sidang-korupsi-ekspor-cpo</t>
+          <t>https://rri.co.id/tahuna/nasional/2749745/tantangan-implementasi-bahan-bakar-biodiesel-b50</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TVRI News</t>
+          <t>RRI.co.id</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>cpo</t>
+          <t>fame, biodiesel</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -6851,21 +6851,21 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46287.13888888889</v>
+        <v>46287.29155092593</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Kejar ketahanan energi, Indonesia konversi batu bara jadi BBM</t>
+          <t>Pertamina Perkuat Distribusi Biodiesel RI Lewat Layanan Maritim</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>https://www.idnfinancials.com/id/news/69208/kejar-ketahanan-energi-indonesia-konversi-batu-bara-jadi-bbm</t>
+          <t>https://www.cnbcindonesia.com/news/20260922135705-4-769891/pertamina-perkuat-distribusi-biodiesel-ri-lewat-layanan-maritim</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>IDNFinancials</t>
+          <t>CNBC Indonesia</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>minyak sawit</t>
+          <t>fame, biodiesel</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -6898,26 +6898,26 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46287.42222222222</v>
+        <v>46287.20275462963</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Tantangan Implementasi Bahan Bakar Biodiesel B50</t>
+          <t>Pertamina Trans Kontinental siap distribusikan biodiesel di Indonesia</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/tahuna/nasional/2749745/tantangan-implementasi-bahan-bakar-biodiesel-b50</t>
+          <t>https://ambon.antaranews.com/berita/344444/pertamina-trans-kontinental-siap-distribusikan-biodiesel-di-indonesia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>RRI.co.id</t>
+          <t>ambon.antaranews.com</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -6945,21 +6945,21 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46287.29155092593</v>
+        <v>46287.25334490741</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Pertamina Perkuat Distribusi Biodiesel RI Lewat Layanan Maritim</t>
+          <t>Biodiesel B50 Jadi Strategi Indonesia Perkuat Industri dan Ketahanan Energi</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnbcindonesia.com/news/20260922135705-4-769891/pertamina-perkuat-distribusi-biodiesel-ri-lewat-layanan-maritim</t>
+          <t>https://esgnow.republika.co.id/berita/tlr4w1370/biodiesel-b50-jadi-strategi-indonesia-perkuat-industri-dan-ketahanan-energi</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>CNBC Indonesia</t>
+          <t>republika.co.id</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>fame, biodiesel</t>
+          <t>biodiesel</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -6992,21 +6992,21 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46287.20275462963</v>
+        <v>46287.575</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Pertamina Trans Kontinental siap distribusikan biodiesel di Indonesia</t>
+          <t>Biodiesel Makin Luas, Pertamina Trans Kontinental Perkuat Konektivitas Laut</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>https://ambon.antaranews.com/berita/344444/pertamina-trans-kontinental-siap-distribusikan-biodiesel-di-indonesia</t>
+          <t>https://money.kompas.com/read/2026/09/22/204800726/biodiesel-makin-luas-pertamina-trans-kontinental-perkuat-konektivitas-laut</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ambon.antaranews.com</t>
+          <t>Kompas.com</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>biodiesel</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -7039,21 +7039,21 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46287.25334490741</v>
+        <v>46287.10900462963</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Biodiesel B50 Jadi Strategi Indonesia Perkuat Industri dan Ketahanan Energi</t>
+          <t>Jurus Pertamina Dorong Distribusi Biodiesel</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>https://esgnow.republika.co.id/berita/tlr4w1370/biodiesel-b50-jadi-strategi-indonesia-perkuat-industri-dan-ketahanan-energi</t>
+          <t>https://finance.detik.com/energi/d-8673459/jurus-pertamina-dorong-distribusi-biodiesel</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>republika.co.id</t>
+          <t>detikFinance</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7086,21 +7086,21 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46287.575</v>
+        <v>46287.10305555556</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Biodiesel Makin Luas, Pertamina Trans Kontinental Perkuat Konektivitas Laut</t>
+          <t>Pertamina Trans Kontinental Perkuat Logistik Laut untuk Distribusi Biodiesel</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>https://money.kompas.com/read/2026/09/22/204800726/biodiesel-makin-luas-pertamina-trans-kontinental-perkuat-konektivitas-laut</t>
+          <t>https://ekonomi.bisnis.com/read/20260922/98/2006270/pertamina-trans-kontinental-perkuat-logistik-laut-untuk-distribusi-biodiesel</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Kompas.com</t>
+          <t>Bisnis.com - Ekonomi</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7133,21 +7133,21 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46287.10900462963</v>
+        <v>46287.9262037037</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jurus Pertamina Dorong Distribusi Biodiesel</t>
+          <t>Wamenlu: Program Biodiesel Perkuat Posisi Indonesia dalam Ketahanan Energi Global</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8673459/jurus-pertamina-dorong-distribusi-biodiesel</t>
+          <t>https://www.tribunnews.com/internasional/7886360/wamenlu-program-biodiesel-perkuat-posisi-indonesia-dalam-ketahanan-energi-global</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>detikFinance</t>
+          <t>Tribunnews.com</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7180,21 +7180,21 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46287.10305555556</v>
+        <v>46287.16935185185</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pertamina Trans Kontinental Perkuat Logistik Laut untuk Distribusi Biodiesel</t>
+          <t>Aprobi: Pengembangan BBN berbasis sawit efektif kurangi impor BBM</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>https://ekonomi.bisnis.com/read/20260922/98/2006270/pertamina-trans-kontinental-perkuat-logistik-laut-untuk-distribusi-biodiesel</t>
+          <t>https://www.antaranews.com/berita/5752256/aprobi-pengembangan-bbn-berbasis-sawit-efektif-kurangi-impor-bbm</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Bisnis.com - Ekonomi</t>
+          <t>ANTARA News</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>biodiesel</t>
+          <t>biodiesel, sawit</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -7227,26 +7227,26 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46287.06944444445</v>
+        <v>46287.31553240741</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Berita Video - Peremajaan Sawit Jadi Penopang Pasokan Biodiesel B50</t>
+          <t>PTK Perkuat Logistik Maritim untuk Distribusi Biodiesel</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/pontianak/berita-video/49953/peremajaan-sawit-jadi-penopang-pasokan-biodiesel-b50</t>
+          <t>https://www.idntimes.com/business/economy/ptk-perkuat-logistik-maritim-untuk-distribusi-biodiesel-00-gshdq-6r1wb1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>RRI.co.id</t>
+          <t>IDN Times</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -7274,21 +7274,21 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46287.9262037037</v>
+        <v>46287.07810185185</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Wamenlu: Program Biodiesel Perkuat Posisi Indonesia dalam Ketahanan Energi Global</t>
+          <t>Dari B2,5 hingga B30, Begini Perjalanan Distribusi Biodiesel Pertamina - Suara Merdeka</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>https://www.tribunnews.com/internasional/7886360/wamenlu-program-biodiesel-perkuat-posisi-indonesia-dalam-ketahanan-energi-global</t>
+          <t>https://www.suaramerdeka.com/ekonomi/0417663258/dari-b25-hingga-b30-begini-perjalanan-distribusi-biodiesel-pertamina</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Tribunnews.com</t>
+          <t>suaramerdeka.com</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7321,21 +7321,21 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46287.16935185185</v>
+        <v>46287.40177083333</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Aprobi: Pengembangan BBN berbasis sawit efektif kurangi impor BBM</t>
+          <t>Bukan Cuma Soal Energi, Wamenlu Ungkap Strategi RI Dorong Biodiesel Sawit</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5752256/aprobi-pengembangan-bbn-berbasis-sawit-efektif-kurangi-impor-bbm</t>
+          <t>https://akurat.co/riil/892841/bukan-cuma-soal-energi-wamenlu-ungkap-strategi-ri-dorong-biodiesel-sawit</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ANTARA News</t>
+          <t>Akurat.co</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7368,21 +7368,21 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46287.08625</v>
+        <v>46287.52574074074</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Pertamina Trans Kontinental Perkuat Distribusi Biodiesel di Indonesia</t>
+          <t>Bioetanol Lagi, Target Besar, Progres Masih Kecil Halaman 1</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>https://ekbis.sindonews.com/read/1752327/34/pertamina-trans-kontinental-perkuat-distribusi-biodiesel-di-indonesia-1790042996</t>
+          <t>https://www.kompasiana.com/karnitakar4943/6ab1ce4434777c636138b442/bioetanol-lagi-target-besar-progres-masih-kecil</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>SINDOnews Ekbis</t>
+          <t>kompasiana.com</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7415,21 +7415,21 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46287.31553240741</v>
+        <v>46287.85431712963</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PTK Perkuat Logistik Maritim untuk Distribusi Biodiesel</t>
+          <t>Siapkan Roadmap BBN E50, Bahlil Dorong Produksi Etanol Dalam Negeri</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>https://www.idntimes.com/business/economy/ptk-perkuat-logistik-maritim-untuk-distribusi-biodiesel-00-gshdq-6r1wb1</t>
+          <t>https://www.cnnindonesia.com/ekonomi/20260922015750-85-1406565/siapkan-roadmap-bbn-e50-bahlil-dorong-produksi-etanol-dalam-negeri</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>IDN Times</t>
+          <t>cnnindonesia.com</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7462,21 +7462,21 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46287.07810185185</v>
+        <v>46287.34083333334</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dari B2,5 hingga B30, Begini Perjalanan Distribusi Biodiesel Pertamina - Suara Merdeka</t>
+          <t>Distribusi Biodiesel Antarpulau Diperkuat Jaringan Logistik Maritim</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>https://www.suaramerdeka.com/ekonomi/0417663258/dari-b25-hingga-b30-begini-perjalanan-distribusi-biodiesel-pertamina</t>
+          <t>https://economy.okezone.com/read/2026/09/22/320/3243521/distribusi-biodiesel-antarpulau-diperkuat-jaringan-logistik-maritim</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>suaramerdeka.com</t>
+          <t>economy.okezone.com</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7509,21 +7509,21 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46287.40177083333</v>
+        <v>46287.32638888889</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Bukan Cuma Soal Energi, Wamenlu Ungkap Strategi RI Dorong Biodiesel Sawit</t>
+          <t>Pemerintah Siapkan Pengembangan E50, Pengusaha Soroti Kesiapan Infrastruktur</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>https://akurat.co/riil/892841/bukan-cuma-soal-energi-wamenlu-ungkap-strategi-ri-dorong-biodiesel-sawit</t>
+          <t>https://hijau.bisnis.com/read/20260922/652/2006052/pemerintah-siapkan-pengembangan-e50-pengusaha-soroti-kesiapan-infrastruktur</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Akurat.co</t>
+          <t>Bisnis.com</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>biodiesel, sawit</t>
+          <t>biodiesel</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -7556,21 +7556,21 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46287.52574074074</v>
+        <v>46287.20197916667</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Bioetanol Lagi, Target Besar, Progres Masih Kecil Halaman 1</t>
+          <t>BCA Sekuritas</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompasiana.com/karnitakar4943/6ab1ce4434777c636138b442/bioetanol-lagi-target-besar-progres-masih-kecil</t>
+          <t>https://bcasekuritas.co.id/latest-news/news/pertamina-trans-kontinental-siap-distribusikan-biodiesel-di-indonesia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>kompasiana.com</t>
+          <t>BCA Sekuritas</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>biodiesel</t>
+          <t>biodiesel, industri agro, pejabat_presisi, sawit, pejabat_kemenperin</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -7603,26 +7603,26 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46287.85431712963</v>
+        <v>46287.27708333333</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Siapkan Roadmap BBN E50, Bahlil Dorong Produksi Etanol Dalam Negeri</t>
+          <t>Indonesia Prepares Up to 2 Million Hectares for Bioethanol Feedstock</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnnindonesia.com/ekonomi/20260922015750-85-1406565/siapkan-roadmap-bbn-e50-bahlil-dorong-produksi-etanol-dalam-negeri</t>
+          <t>https://jakartaglobe.id/business/indonesia-prepares-up-to-2-million-hectares-for-bioethanol-feedstock</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>cnnindonesia.com</t>
+          <t>Jakarta Globe</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>biodiesel</t>
+          <t>bioethanol</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -7650,21 +7650,21 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46287.34083333334</v>
+        <v>46287.5375</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Distribusi Biodiesel Antarpulau Diperkuat Jaringan Logistik Maritim</t>
+          <t>Pemkab Garut Siapkan 15 Ribu Ha Lahan Jagung untuk Bahan Baku Energi Bioethanol</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>https://economy.okezone.com/read/2026/09/22/320/3243521/distribusi-biodiesel-antarpulau-diperkuat-jaringan-logistik-maritim</t>
+          <t>https://rri.co.id/bandung/regional/2750798/pemkab-garut-siapkan-15-ribu-ha-lahan-jagung-untuk-bahan-baku-energi-bioethanol</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>economy.okezone.com</t>
+          <t>RRI.co.id</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>biodiesel</t>
+          <t>bioethanol</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -7697,21 +7697,21 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46287.32638888889</v>
+        <v>46287.50871527778</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Pemerintah Siapkan Pengembangan E50, Pengusaha Soroti Kesiapan Infrastruktur</t>
+          <t>Farmers Protest Sugar Imports, Agriculture Minister Busy with Bioethanol</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>https://hijau.bisnis.com/read/20260922/652/2006052/pemerintah-siapkan-pengembangan-e50-pengusaha-soroti-kesiapan-infrastruktur</t>
+          <t>https://www.kompas.id/artikel/farmers-protest-import-of-raw-sugar-busy-dealing-with-bioethanol?open_from=English_Page</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Bisnis.com</t>
+          <t>kompas.id</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>biodiesel</t>
+          <t>bioethanol</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -7744,21 +7744,21 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46287.20197916667</v>
+        <v>46287.26059027778</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BCA Sekuritas</t>
+          <t>Top! Pertamina Sukses Tekan Emisi Hingga 118%, Lampaui Target Tahunan</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>https://bcasekuritas.co.id/latest-news/news/pertamina-trans-kontinental-siap-distribusikan-biodiesel-di-indonesia</t>
+          <t>https://www.cnbcindonesia.com/news/20260922130828-4-769870/top-pertamina-sukses-tekan-emisi-hingga-118-lampaui-target-tahunan</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>BCA Sekuritas</t>
+          <t>CNBC Indonesia</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>biodiesel</t>
+          <t>bioethanol</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -7791,26 +7791,26 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46287.27708333333</v>
+        <v>46287.48541666667</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Indonesia Prepares Up to 2 Million Hectares for Bioethanol Feedstock</t>
+          <t>Dukung Program Bioethanol Kementan, Pemkab Bone Siapkan Data Potensi Lahan</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>https://jakartaglobe.id/business/indonesia-prepares-up-to-2-million-hectares-for-bioethanol-feedstock</t>
+          <t>https://rri.co.id/bone/regional/2750511/dukung-program-bioethanol-kementan-pemkab-bone-siapkan-data-potensi-lahan</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Jakarta Globe</t>
+          <t>RRI.co.id</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -7838,16 +7838,16 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46287.5375</v>
+        <v>46287.13472222222</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Pemkab Garut Siapkan 15 Ribu Ha Lahan Jagung untuk Bahan Baku Energi Bioethanol</t>
+          <t>Pembahasan Program Khusus Pemerintah untuk Bioethanol, Bupati Minut jadi Peserta</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/bandung/regional/2750798/pemkab-garut-siapkan-15-ribu-ha-lahan-jagung-untuk-bahan-baku-energi-bioethanol</t>
+          <t>https://rri.co.id/manado/regional/2748609/pembahasan-program-khusus-pemerintah-untuk-bioethanol-bupati-minut-jadi-peserta</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7885,26 +7885,26 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46287.50871527778</v>
+        <v>46287.17862268518</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Farmers Protest Sugar Imports, Agriculture Minister Busy with Bioethanol</t>
+          <t>Garut Siapkan 27.000 Hektare Lahan untuk Bioethanol</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompas.id/artikel/farmers-protest-import-of-raw-sugar-busy-dealing-with-bioethanol?open_from=English_Page</t>
+          <t>https://bandung.bisnis.com/read/20260922/549/2006094/garut-siapkan-27000-hektare-lahan-untuk-bioethanol</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>kompas.id</t>
+          <t>Bisnis.com</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -7932,21 +7932,21 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46287.26059027778</v>
+        <v>46287.51666666667</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Top! Pertamina Sukses Tekan Emisi Hingga 118%, Lampaui Target Tahunan</t>
+          <t>Bupati Gorut dan Mentan Bahas Pengembangan Bioethanol Nasional</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnbcindonesia.com/news/20260922130828-4-769870/top-pertamina-sukses-tekan-emisi-hingga-118-lampaui-target-tahunan</t>
+          <t>https://rri.co.id/gorontalo/asta-cita/2749046/bupati-gorut-dan-mentan-bahas-pengembangan-bioethanol-nasional</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>CNBC Indonesia</t>
+          <t>RRI.co.id</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7979,16 +7979,16 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46287.48541666667</v>
+        <v>46287.30416666667</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dukung Program Bioethanol Kementan, Pemkab Bone Siapkan Data Potensi Lahan</t>
+          <t>Wakil Bupati Boalemo Bahas Peluang Pengembangan Bioethanol dengan Mentan RI</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/bone/regional/2750511/dukung-program-bioethanol-kementan-pemkab-bone-siapkan-data-potensi-lahan</t>
+          <t>https://rri.co.id/gorontalo/info-pemda/2749673/wakil-bupati-boalemo-bahas-peluang-pengembangan-bioethanol-dengan-mentan-ri</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -8026,16 +8026,16 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46287.13472222222</v>
+        <v>46287.35138888889</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Pembahasan Program Khusus Pemerintah untuk Bioethanol, Bupati Minut jadi Peserta</t>
+          <t>Pabrik Bioetanol Bakal Dibangun di Garut, Bupati Dorong Budidaya Singkong</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/manado/regional/2748609/pembahasan-program-khusus-pemerintah-untuk-bioethanol-bupati-minut-jadi-peserta</t>
+          <t>https://rri.co.id/bandung/regional/2749724/pabrik-bioetanol-bakal-dibangun-di-garut-bupati-dorong-budidaya-singkong</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8073,26 +8073,26 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46287.17862268518</v>
+        <v>46287.27986111111</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Garut Siapkan 27.000 Hektare Lahan untuk Bioethanol</t>
+          <t>Bupati Gowa Tak Ada Saat Kantor dan Rujab Digeledah Terkait Korupsi PBG, Ini Alasannya</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>https://bandung.bisnis.com/read/20260922/549/2006094/garut-siapkan-27000-hektare-lahan-untuk-bioethanol</t>
+          <t>https://makassar.kompas.com/read/2026/09/22/134300578/bupati-gowa-tak-ada-saat-kantor-dan-rujab-digeledah-terkait-korupsi-pbg-ini</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Bisnis.com</t>
+          <t>Kompas.com</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -8120,21 +8120,21 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46287.51666666667</v>
+        <v>46287.02717592593</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Bupati Gorut dan Mentan Bahas Pengembangan Bioethanol Nasional</t>
+          <t>Berita Daerah || Kabupaten Garut Siap Dukung Ketahanan Energi Nasional melalui Program Bioethanol</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/gorontalo/asta-cita/2749046/bupati-gorut-dan-mentan-bahas-pengembangan-bioethanol-nasional</t>
+          <t>https://www.garutkab.go.id/berita/kabupaten-garut-siap-dukung-ketahanan-energi-nasional-melalui-program-bioethanol-1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>RRI.co.id</t>
+          <t>Pemerintah Kabupaten Garut</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8167,16 +8167,16 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46287.30416666667</v>
+        <v>46287.33611111111</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Wakil Bupati Boalemo Bahas Peluang Pengembangan Bioethanol dengan Mentan RI</t>
+          <t>Komisi II Dorong Realisasi Jagung SPHP untuk Peternak Mandiri</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/gorontalo/info-pemda/2749673/wakil-bupati-boalemo-bahas-peluang-pengembangan-bioethanol-dengan-mentan-ri</t>
+          <t>https://rri.co.id/gorontalo/info-pemda/2747973/komisi-ii-dorong-realisasi-jagung-sphp-untuk-peternak-mandiri</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>bioethanol</t>
+          <t>pakan ternak</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -8214,26 +8214,26 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46287.35138888889</v>
+        <v>46287.2944212963</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Pabrik Bioetanol Bakal Dibangun di Garut, Bupati Dorong Budidaya Singkong</t>
+          <t>Budidaya maggot di Sangatta manfaatkan limbah SPPG</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/bandung/regional/2749724/pabrik-bioetanol-bakal-dibangun-di-garut-bupati-dorong-budidaya-singkong</t>
+          <t>https://kaltim.antaranews.com/berita/267407/budidaya-maggot-di-sangatta-manfaatkan-limbah-sppg</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>RRI.co.id</t>
+          <t>ANTARA News</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>bioethanol</t>
+          <t>pakan ternak</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -8261,26 +8261,26 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46287.27986111111</v>
+        <v>46287.325</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Bupati Gowa Tak Ada Saat Kantor dan Rujab Digeledah Terkait Korupsi PBG, Ini Alasannya</t>
+          <t>Ile Ape dan Ile Ape Timur Hadapi Dampak Ganda pada Pertanian</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>https://makassar.kompas.com/read/2026/09/22/134300578/bupati-gowa-tak-ada-saat-kantor-dan-rujab-digeledah-terkait-korupsi-pbg-ini</t>
+          <t>https://rri.co.id/ende/asta-cita/2749519/ile-ape-dan-ile-ape-timur-hadapi-dampak-ganda-pada-pertanian</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Kompas.com</t>
+          <t>RRI.co.id</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>bioethanol</t>
+          <t>pakan ternak</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -8308,26 +8308,26 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46287.06063657408</v>
+        <v>46287.43989583333</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Garuda - Garba Rujukan Digital</t>
+          <t>Mahasiswa Teknologi Pakan Ternak Selesaikan Program Magang di BRMP RB</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>https://garuda.kemdiktisaintek.go.id/documents/detail/6719154</t>
+          <t>https://prodi.unhas.ac.id/sarjana-terapan-teknologi-pakan-ternak/post/show/id/mahasiswa-teknologi-pakan-ternak-selesaikan-program-magang-di-brmp-rb</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Garuda - Garba Rujukan Digital</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>bioethanol</t>
+          <t>pakan ternak</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -8355,21 +8355,21 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46287.02717592593</v>
+        <v>46287.18490740741</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Berita Daerah || Kabupaten Garut Siap Dukung Ketahanan Energi Nasional melalui Program Bioethanol</t>
+          <t>Indonesia-Bulgaria Perkuat Kerja Sama Industri, Ekspor dan Investasi</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>https://www.garutkab.go.id/berita/kabupaten-garut-siap-dukung-ketahanan-energi-nasional-melalui-program-bioethanol-1</t>
+          <t>https://www.tribunnews.com/bisnis/7885987/indonesia-bulgaria-perkuat-kerja-sama-industri-ekspor-dan-investasi</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten Garut</t>
+          <t>Tribunnews.com</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8377,21 +8377,29 @@
           <t>Positif</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Faisol Riza</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Tri Supondy</t>
+        </is>
+      </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>WAMEN</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>bioethanol</t>
+          <t>industri agro</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -8402,21 +8410,21 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46287.33611111111</v>
+        <v>46287.35902777778</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Komisi II Dorong Realisasi Jagung SPHP untuk Peternak Mandiri</t>
+          <t>HIPMI Ungkap 5 Ruang Kolaborasi Industri Alat Berat dengan Pengusaha Lokal</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/gorontalo/info-pemda/2747973/komisi-ii-dorong-realisasi-jagung-sphp-untuk-peternak-mandiri</t>
+          <t>https://wartaekonomi.co.id/read636193/hipmi-ungkap-5-ruang-kolaborasi-industri-alat-berat-dengan-pengusaha-lokal</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>RRI.co.id</t>
+          <t>wartaekonomi.co.id</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8424,21 +8432,25 @@
           <t>Positif</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MENTERI</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>pakan ternak</t>
+          <t>industri agro, pejabat_presisi</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -8449,43 +8461,47 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46287.2944212963</v>
+        <v>46287.08144675926</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Budidaya maggot di Sangatta manfaatkan limbah SPPG</t>
+          <t>RI-Bulgaria Perluas Kerja Sama Industri, Investasi Manufaktur Jadi Fokus</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>https://kaltim.antaranews.com/berita/267407/budidaya-maggot-di-sangatta-manfaatkan-limbah-sppg</t>
+          <t>https://akurat.co/riil/892710/ri-bulgaria-perluas-kerja-sama-industri-investasi-manufaktur-jadi-fokus</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ANTARA News</t>
+          <t>Akurat.co</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Netral</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr"/>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Faisol Riza</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>WAMEN</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>pakan ternak</t>
+          <t>industri agro</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -8496,21 +8512,21 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46287.325</v>
+        <v>46287.45765046297</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ile Ape dan Ile Ape Timur Hadapi Dampak Ganda pada Pertanian</t>
+          <t>39.184 UMKM Kaltim Belum Kantongi Sertifikat Halal Jelang Tenggat Oktober 2026</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/ende/asta-cita/2749519/ile-ape-dan-ile-ape-timur-hadapi-dampak-ganda-pada-pertanian</t>
+          <t>https://kalimantan.bisnis.com/read/20260922/408/2006241/39184-umkm-kaltim-belum-kantongi-sertifikat-halal-jelang-tenggat-oktober-2026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>RRI.co.id</t>
+          <t>Bisnis.com</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8532,7 +8548,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>pakan ternak</t>
+          <t>makanan dan minuman</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -8543,21 +8559,21 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46287.43989583333</v>
+        <v>46287.35619212963</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mahasiswa Teknologi Pakan Ternak Selesaikan Program Magang di BRMP RB</t>
+          <t>Beri Energi Baru Menuju UMK Maju, Pertamina Patra Niaga Gelar Pelatihan Perdana UMK Academy 2026</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>https://prodi.unhas.ac.id/sarjana-terapan-teknologi-pakan-ternak/post/show/id/mahasiswa-teknologi-pakan-ternak-selesaikan-program-magang-di-brmp-rb</t>
+          <t>https://www.suarasurabaya.net/ekonomibisnis/2026/beri-energi-baru-menuju-umk-maju-pertamina-patra-niaga-gelar-pelatihan-perdana-umk-academy-2026/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Suara Surabaya</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8579,7 +8595,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>pakan ternak</t>
+          <t>makanan dan minuman</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -8590,51 +8606,43 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46287.18490740741</v>
+        <v>46287.34434027778</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Indonesia-Bulgaria Perkuat Kerja Sama Industri, Ekspor dan Investasi</t>
+          <t>Terekam! Warga Seenaknya Buang Sampah di Belakang Kantor Kecamatan Krian</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>https://www.tribunnews.com/bisnis/7885987/indonesia-bulgaria-perkuat-kerja-sama-industri-ekspor-dan-investasi</t>
+          <t>https://www.detik.com/jatim/berita/d-8673899/terekam-warga-seenaknya-buang-sampah-di-belakang-kantor-kecamatan-krian</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Tribunnews.com</t>
+          <t>detikcom</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Positif</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Faisol Riza</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Tri Supondy</t>
-        </is>
-      </c>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>WAMEN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>industri agro</t>
+          <t>makanan dan minuman</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -8645,21 +8653,21 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46287.35902777778</v>
+        <v>46287.63712962963</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HIPMI Ungkap 5 Ruang Kolaborasi Industri Alat Berat dengan Pengusaha Lokal</t>
+          <t>BI NTT: FCE 2026 mendorong inovasi dan daya saing UMKM</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>https://wartaekonomi.co.id/read636193/hipmi-ungkap-5-ruang-kolaborasi-industri-alat-berat-dengan-pengusaha-lokal</t>
+          <t>https://kupang.antaranews.com/berita/200349/bi-ntt-fce-2026-mendorong-inovasi-dan-daya-saing-umkm</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>wartaekonomi.co.id</t>
+          <t>ANTARA News</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8667,25 +8675,21 @@
           <t>Positif</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Agus Gumiwang Kartasasmita</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>MENTERI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>industri agro</t>
+          <t>makanan dan minuman</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -8696,16 +8700,16 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46287.08144675926</v>
+        <v>46287.04380787037</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>RI-Bulgaria Perluas Kerja Sama Industri, Investasi Manufaktur Jadi Fokus</t>
+          <t>El Nino Bisa Tekan Kualitas Kredit, OJK Minta Perbankan Siapkan Langkah Antisipasi</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>https://akurat.co/riil/892710/ri-bulgaria-perluas-kerja-sama-industri-investasi-manufaktur-jadi-fokus</t>
+          <t>https://akurat.co/keuangan/892695/el-nino-bisa-tekan-kualitas-kredit-ojk-minta-perbankan-siapkan-langkah-antisipasi</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8715,28 +8719,24 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Positif</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Faisol Riza</t>
-        </is>
-      </c>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>WAMEN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>industri agro</t>
+          <t>makanan dan minuman</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -8747,21 +8747,21 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46287.03997685185</v>
+        <v>46287.36858796296</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BCA Sekuritas</t>
+          <t>Pertamina Patra Niaga Mulai UMK Academy 2026, Libatkan 217 Pelaku Usaha Jatimbalinus</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>https://bcasekuritas.co.id/latest-news/news/kemenperin-akselerasi-mondernisasi-industri-agro</t>
+          <t>https://surabaya.bisnis.com/read/20260922/532/2006207/pertamina-patra-niaga-mulai-umk-academy-2026-libatkan-217-pelaku-usaha-jatimbalinus</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>BCA Sekuritas</t>
+          <t>Bisnis.com - Surabaya</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -8769,29 +8769,21 @@
           <t>Positif</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>RR Citra Rapati</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Agus Gumiwang Kartasasmita</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>industri agro</t>
+          <t>makanan dan minuman</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -8802,21 +8794,21 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46287.45765046297</v>
+        <v>46287.33873842593</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>39.184 UMKM Kaltim Belum Kantongi Sertifikat Halal Jelang Tenggat Oktober 2026</t>
+          <t>Bukan Sekadar Jualan, 217 UMK Jatimbalinus Dibekali Cara Hitung Harga Jual hingga Arus Kas</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>https://kalimantan.bisnis.com/read/20260922/408/2006241/39184-umkm-kaltim-belum-kantongi-sertifikat-halal-jelang-tenggat-oktober-2026</t>
+          <t>https://surabaya.inews.id/read/717707/bukan-sekadar-jualan-217-umk-jatimbalinus-dibekali-cara-hitung-harga-jual-hingga-arus-kas</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Bisnis.com</t>
+          <t>iNews.ID</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8849,26 +8841,26 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46287.35619212963</v>
+        <v>46287.23125</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Beri Energi Baru Menuju UMK Maju, Pertamina Patra Niaga Gelar Pelatihan Perdana UMK Academy 2026</t>
+          <t>Bagi Roti dan Air ke Massa Demo DPR, Polri Dinilai Tunjukkan Pendekatan Humanis</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>https://www.suarasurabaya.net/ekonomibisnis/2026/beri-energi-baru-menuju-umk-maju-pertamina-patra-niaga-gelar-pelatihan-perdana-umk-academy-2026/</t>
+          <t>https://wartaekonomi.co.id/read636304/bagi-roti-dan-air-ke-massa-demo-dpr-polri-dinilai-tunjukkan-pendekatan-humanis</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Suara Surabaya</t>
+          <t>wartaekonomi.co.id</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -8896,21 +8888,21 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46287.34434027778</v>
+        <v>46287.50515046297</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Terekam! Warga Seenaknya Buang Sampah di Belakang Kantor Kecamatan Krian</t>
+          <t>Sultan Lamongan Gelar Tahlilan Mewah, Tamu Norwati Senyum Bawa Pulang Kipas Angin dan Keranjang</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>https://www.detik.com/jatim/berita/d-8673899/terekam-warga-seenaknya-buang-sampah-di-belakang-kantor-kecamatan-krian</t>
+          <t>https://style.tribunnews.com/news/384257/sultan-lamongan-gelar-tahlilan-mewah-tamu-norwati-senyum-bawa-pulang-kipas-angin-dan-keranjang</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>detikcom</t>
+          <t>TribunStyle.com</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -8943,26 +8935,26 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46287.63712962963</v>
+        <v>46287.01689814815</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BI NTT: FCE 2026 mendorong inovasi dan daya saing UMKM</t>
+          <t>PERLINDUNGAN MUTU MAKANAN DAN MINUMAN DIKOTA BANJARBARU</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>https://kupang.antaranews.com/berita/200349/bi-ntt-fce-2026-mendorong-inovasi-dan-daya-saing-umkm</t>
+          <t>https://jdih.banjarbarukota.go.id/produk-hukum/propemperda-18844319xidprd2015-2016-perlindungan-mutu-makanan-dan-minuman-dikota-banjarbaru-33?from=%2Fpembentukan-perda%3Ftypes%3Dpropemperda%252Cranperda%252Cnaskah-pendukung%252Canalisis-evaluasi%252Crisalah-pembahasan%252Ckajian-hukum%26page%3D10</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ANTARA News</t>
+          <t>JDIH Banjarbaru</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -8990,21 +8982,21 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46287.04380787037</v>
+        <v>46287.1753125</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>El Nino Bisa Tekan Kualitas Kredit, OJK Minta Perbankan Siapkan Langkah Antisipasi</t>
+          <t>Diduga Stres, Tapir di Mesuji Berkeliaran di Perkebunan Sawit</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>https://akurat.co/keuangan/892695/el-nino-bisa-tekan-kualitas-kredit-ojk-minta-perbankan-siapkan-langkah-antisipasi</t>
+          <t>https://news.detik.com/berita/d-8673585/diduga-stres-tapir-di-mesuji-berkeliaran-di-perkebunan-sawit</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Akurat.co</t>
+          <t>detikNews</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -9026,7 +9018,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>makanan dan minuman</t>
+          <t>sawit</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -9037,26 +9029,26 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46287.36858796296</v>
+        <v>46287.21896990741</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Pertamina Patra Niaga Mulai UMK Academy 2026, Libatkan 217 Pelaku Usaha Jatimbalinus</t>
+          <t>Peremajaan Sawit Rakyat di Riau Jangkau 23.789 Pekebun, Dana Tersalur Rp1,9 Triliun</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>https://surabaya.bisnis.com/read/20260922/532/2006207/pertamina-patra-niaga-mulai-umk-academy-2026-libatkan-217-pelaku-usaha-jatimbalinus</t>
+          <t>https://sumatra.bisnis.com/read/20260922/533/2006074/peremajaan-sawit-rakyat-di-riau-jangkau-23789-pekebun-dana-tersalur-rp19-triliun</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Bisnis.com - Surabaya</t>
+          <t>Bisnis.com</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -9073,7 +9065,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>makanan dan minuman</t>
+          <t>sawit</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -9084,26 +9076,26 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46287.33873842593</v>
+        <v>46287.57351851852</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bukan Sekadar Jualan, 217 UMK Jatimbalinus Dibekali Cara Hitung Harga Jual hingga Arus Kas</t>
+          <t>Bos Perusahaan Sawit Handoko Limaho dan Liu Raymond Divonis 9 Tahun Penjara</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>https://surabaya.inews.id/read/717707/bukan-sekadar-jualan-217-umk-jatimbalinus-dibekali-cara-hitung-harga-jual-hingga-arus-kas</t>
+          <t>https://www.kompas.id/artikel/kasus-korupsi-lpei-bos-perusahaan-sawit-handoko-limaho-divonis-9-tahun-penjara</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>iNews.ID</t>
+          <t>kompas.id</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -9120,7 +9112,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>makanan dan minuman</t>
+          <t>sawit</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -9131,26 +9123,26 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46287.23125</v>
+        <v>46287.35840277778</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Bagi Roti dan Air ke Massa Demo DPR, Polri Dinilai Tunjukkan Pendekatan Humanis</t>
+          <t>Realisasi Program Peremajaan Sawit Rakyat di Riau baru capai 55.140 hektare sejak 2017</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>https://wartaekonomi.co.id/read636304/bagi-roti-dan-air-ke-massa-demo-dpr-polri-dinilai-tunjukkan-pendekatan-humanis</t>
+          <t>https://riau.antaranews.com/berita/453491/realisasi-program-peremajaan-sawit-rakyat-di-riau-baru-capai-55140-hektare-sejak-2017</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>wartaekonomi.co.id</t>
+          <t>ANTARA News Riau</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -9167,7 +9159,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>makanan dan minuman</t>
+          <t>sawit</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -9178,26 +9170,26 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46287.50515046297</v>
+        <v>46287.24859953704</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Sultan Lamongan Gelar Tahlilan Mewah, Tamu Norwati Senyum Bawa Pulang Kipas Angin dan Keranjang</t>
+          <t>Nilai Ekspor Komoditas Sawit Indonesia Meningkat pada Semester I 2026</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>https://style.tribunnews.com/news/384257/sultan-lamongan-gelar-tahlilan-mewah-tamu-norwati-senyum-bawa-pulang-kipas-angin-dan-keranjang</t>
+          <t>https://databoks.katadata.co.id/perdagangan/statistik/6ab209e4502cc/nilai-ekspor-komoditas-sawit-indonesia-meningkat-pada-semester-i-2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TribunStyle.com</t>
+          <t>Databoks Katadata</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -9214,7 +9206,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>makanan dan minuman</t>
+          <t>sawit</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -9225,21 +9217,21 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46287.01689814815</v>
+        <v>46287.43112268519</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PERLINDUNGAN MUTU MAKANAN DAN MINUMAN DIKOTA BANJARBARU</t>
+          <t>Ironi Menjadi Maba di Jogja: Dicap Aneh dan Dimanfaatkan Teman karena Dikira Kaya Hanya Karena Berasal dari Jambi</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>https://jdih.banjarbarukota.go.id/produk-hukum/propemperda-18844319xidprd2015-2016-perlindungan-mutu-makanan-dan-minuman-dikota-banjarbaru-33?from=%2Fpembentukan-perda%3Ftypes%3Dpropemperda%252Cranperda%252Cnaskah-pendukung%252Canalisis-evaluasi%252Crisalah-pembahasan%252Ckajian-hukum%26page%3D10</t>
+          <t>https://mojok.co/liputan/sekolahan/maba-di-jogja-asal-jambi-dicap-aneh-dan-kaya/</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>JDIH Banjarbaru</t>
+          <t>Mojok.co</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -9261,7 +9253,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>makanan dan minuman</t>
+          <t>sawit</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -9272,26 +9264,26 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46287.1753125</v>
+        <v>46287.15347222222</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Diduga Stres, Tapir di Mesuji Berkeliaran di Perkebunan Sawit</t>
+          <t>Giliran 2 Eks Pejabat LPEI dan 2 Bos Sawit Hadapi Vonis Kasus Rp992,82 Miliar</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>https://news.detik.com/berita/d-8673585/diduga-stres-tapir-di-mesuji-berkeliaran-di-perkebunan-sawit</t>
+          <t>https://www.inilah.com/giliran-2-eks-pejabat-lpei-dan-2-bos-sawit-hadapi-vonis-kasus-rp99282-miliar</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>detikNews</t>
+          <t>inilah.com</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -9319,21 +9311,21 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46287.21896990741</v>
+        <v>46287.20347222222</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Peremajaan Sawit Rakyat di Riau Jangkau 23.789 Pekebun, Dana Tersalur Rp1,9 Triliun</t>
+          <t>Warga Mesuji Temukan Tapir Dilindungi di Kebun Sawit</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>https://sumatra.bisnis.com/read/20260922/533/2006074/peremajaan-sawit-rakyat-di-riau-jangkau-23789-pekebun-dana-tersalur-rp19-triliun</t>
+          <t>https://rri.co.id/bandar-lampung/regional/2748630/warga-mesuji-temukan-tapir-dilindungi-di-kebun-sawit</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Bisnis.com</t>
+          <t>RRI.co.id</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9366,26 +9358,26 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46287.57351851852</v>
+        <v>46287.02163194444</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Bos Perusahaan Sawit Handoko Limaho dan Liu Raymond Divonis 9 Tahun Penjara</t>
+          <t>BKSDA Evakuasi Tapir Terjebak di Saluran Air Perkebunan Sawit</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompas.id/artikel/kasus-korupsi-lpei-bos-perusahaan-sawit-handoko-limaho-divonis-9-tahun-penjara</t>
+          <t>https://mediaindonesia.com/nusantara/936014/bksda-evakuasi-tapir-terjebak-di-saluran-air-perkebunan-sawit</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>kompas.id</t>
+          <t>Media Indonesia</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -9413,21 +9405,21 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46287.35840277778</v>
+        <v>46287.04467592593</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Realisasi Program Peremajaan Sawit Rakyat di Riau baru capai 55.140 hektare sejak 2017</t>
+          <t>Harga Sawit Pecah Rekor, di Petani Aceh Singkil Tembus Rp 2.900 Per Kg</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>https://riau.antaranews.com/berita/453491/realisasi-program-peremajaan-sawit-rakyat-di-riau-baru-capai-55140-hektare-sejak-2017</t>
+          <t>https://aceh.tribunnews.com/nanggroe/1044953/harga-sawit-pecah-rekor-di-petani-aceh-singkil-tembus-rp-2900-per-kg</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ANTARA News Riau</t>
+          <t>Serambinews.com</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -9460,16 +9452,16 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46287.24859953704</v>
+        <v>46287.54166666666</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Nilai Ekspor Komoditas Sawit Indonesia Meningkat pada Semester I 2026</t>
+          <t>Konflik Agraria Sektor Perkebunan Indonesia 2025, Terbanyak dari Sawit</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>https://databoks.katadata.co.id/perdagangan/statistik/6ab209e4502cc/nilai-ekspor-komoditas-sawit-indonesia-meningkat-pada-semester-i-2026</t>
+          <t>https://databoks.katadata.co.id/lingkungan/statistik/6ab2c3e12feeb/konflik-agraria-sektor-perkebunan-indonesia-2025-terbanyak-dari-sawit</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9479,7 +9471,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -9507,26 +9499,26 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46287.43112268519</v>
+        <v>46287.22013888889</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Ironi Menjadi Maba di Jogja: Dicap Aneh dan Dimanfaatkan Teman karena Dikira Kaya Hanya Karena Berasal dari Jambi</t>
+          <t>Dugaan Modus Lahan Sawit Fiktif di Kasus LPEI Masuki Babak Vonis, Empat Terdakwa Bersiap</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>https://mojok.co/liputan/sekolahan/maba-di-jogja-asal-jambi-dicap-aneh-dan-kaya/</t>
+          <t>https://www.goriau.com/berita/baca/dugaan-modus-lahan-sawit-fiktif-di-kasus-lpei-masuki-babak-vonis-empat-terdakwa-bersiap.html</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Mojok.co</t>
+          <t>GoRiau.com</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -9554,26 +9546,26 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46287.15347222222</v>
+        <v>46287.50763888889</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Giliran 2 Eks Pejabat LPEI dan 2 Bos Sawit Hadapi Vonis Kasus Rp992,82 Miliar</t>
+          <t>Waspada Ular Bersembunyi di Perkebunan Sawit, Ini Tips Keselamatan bagi Pekerja Kebun - radartv.disway.id</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>https://www.inilah.com/giliran-2-eks-pejabat-lpei-dan-2-bos-sawit-hadapi-vonis-kasus-rp99282-miliar</t>
+          <t>https://radartv.disway.id/peristiwa/read/39638/waspada-ular-bersembunyi-di-perkebunan-sawit-ini-tips-keselamatan-bagi-pekerja-kebun</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>inilah.com</t>
+          <t>Disway</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -9601,26 +9593,26 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46287.20347222222</v>
+        <v>46287.12262731481</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Warga Mesuji Temukan Tapir Dilindungi di Kebun Sawit</t>
+          <t>Aspekpir-BPDP Gelar Workshop Biochar dan Briket Sawit, Dorong Perdagangan Karbon</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/bandar-lampung/regional/2748630/warga-mesuji-temukan-tapir-dilindungi-di-kebun-sawit</t>
+          <t>https://jakarta.suaramerdeka.com/ekonomi/13417663509/aspekpir-bpdp-gelar-workshop-biochar-dan-briket-sawit-dorong-perdagangan-karbon</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>RRI.co.id</t>
+          <t>Suara Merdeka Jakarta</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -9648,26 +9640,26 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46287.02163194444</v>
+        <v>46287.40347222222</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>BKSDA Evakuasi Tapir Terjebak di Saluran Air Perkebunan Sawit</t>
+          <t>Pekerja Pabrik Sawit PT APS, Alami Kecelakaan Kerja Luka Bakar 45 Persen Dirujuk ke RSUD HM Rabaian - palpos.disway.id</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>https://mediaindonesia.com/nusantara/936014/bksda-evakuasi-tapir-terjebak-di-saluran-air-perkebunan-sawit</t>
+          <t>https://palpos.disway.id/muara-enim/read/721865/pekerja-pabrik-sawit-pt-aps-alami-kecelakaan-kerja-luka-bakar-45-persen-dirujuk-ke-rsud-hm-rabaian</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Media Indonesia</t>
+          <t>Palpos</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -9695,26 +9687,26 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46287.04467592593</v>
+        <v>46287.06454861111</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Harga Sawit Pecah Rekor, di Petani Aceh Singkil Tembus Rp 2.900 Per Kg</t>
+          <t>Buah Sawit Bukit Luik Desa Penagan Bangka Dijual ke PT</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>https://aceh.tribunnews.com/nanggroe/1044953/harga-sawit-pecah-rekor-di-petani-aceh-singkil-tembus-rp-2900-per-kg</t>
+          <t>https://bangka.tribunnews.com/lokal/1697101/buah-sawit-bukit-luik-desa-penagan-bangka-dijual-ke-pt</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Serambinews.com</t>
+          <t>Bangkapos.com</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -9742,21 +9734,21 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46287.54166666666</v>
+        <v>46287.5831712963</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Konflik Agraria Sektor Perkebunan Indonesia 2025, Terbanyak dari Sawit</t>
+          <t>Suami Diduga Selingkuh dengan Oknum PNS, Bos Sawit Menggala Bakal Lapor Polisi</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>https://databoks.katadata.co.id/lingkungan/statistik/6ab2c3e12feeb/konflik-agraria-sektor-perkebunan-indonesia-2025-terbanyak-dari-sawit</t>
+          <t>https://lampung.tribunnews.com/lampung/1218891/suami-diduga-selingkuh-dengan-oknum-pns-bos-sawit-menggala-bakal-lapor-polisi</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Databoks Katadata</t>
+          <t>Tribunlampung.co.id</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9789,21 +9781,21 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46287.22013888889</v>
+        <v>46287.65401620371</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Dugaan Modus Lahan Sawit Fiktif di Kasus LPEI Masuki Babak Vonis, Empat Terdakwa Bersiap</t>
+          <t>Bos Sawit Handoko Limaho Divonis 9 Tahun Penjara atas Kasus Korupsi LPEI Rp992 Miliar</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>https://www.goriau.com/berita/baca/dugaan-modus-lahan-sawit-fiktif-di-kasus-lpei-masuki-babak-vonis-empat-terdakwa-bersiap.html</t>
+          <t>https://www.tribunnews.com/nasional/7886343/bos-sawit-handoko-limaho-divonis-9-tahun-penjara-atas-kasus-korupsi-lpei-rp992-miliar</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>GoRiau.com</t>
+          <t>Tribunnews.com</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9836,26 +9828,26 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46287.50763888889</v>
+        <v>46287.39513888889</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Waspada Ular Bersembunyi di Perkebunan Sawit, Ini Tips Keselamatan bagi Pekerja Kebun - radartv.disway.id</t>
+          <t>BRIN Siapkan Inovasi Limbah Nanas dan Sawit untuk Tekstil dan UMKM</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>https://radartv.disway.id/peristiwa/read/39638/waspada-ular-bersembunyi-di-perkebunan-sawit-ini-tips-keselamatan-bagi-pekerja-kebun</t>
+          <t>https://www.tribunnews.com/nasional/7886184/brin-siapkan-inovasi-limbah-nanas-dan-sawit-untuk-tekstil-dan-umkm</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Disway</t>
+          <t>Tribunnews.com</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -9883,26 +9875,26 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46287.12262731481</v>
+        <v>46287.33842592593</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Aspekpir-BPDP Gelar Workshop Biochar dan Briket Sawit, Dorong Perdagangan Karbon</t>
+          <t>Negara Melawan Oligarki Fosil Melalui Sawit: Sosialisme Kedaulatan Energi Nasional</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>https://jakarta.suaramerdeka.com/ekonomi/13417663509/aspekpir-bpdp-gelar-workshop-biochar-dan-briket-sawit-dorong-perdagangan-karbon</t>
+          <t>https://www.tribunnews.com/tribunners/7886117/negara-melawan-oligarki-fosil-melalui-sawit-sosialisme-kedaulatan-energi-nasional</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Suara Merdeka Jakarta</t>
+          <t>Tribunnews.com</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -9930,21 +9922,21 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46287.40347222222</v>
+        <v>46287.68135416666</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Pekerja Pabrik Sawit PT APS, Alami Kecelakaan Kerja Luka Bakar 45 Persen Dirujuk ke RSUD HM Rabaian - palpos.disway.id</t>
+          <t>Sidang Kasus Korupsi LPEI Rp 992 Miliar, Bos Perusahaan Sawit Handoko Limaho Divonis 9 Tahun Penjara</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>https://palpos.disway.id/muara-enim/read/721865/pekerja-pabrik-sawit-pt-aps-alami-kecelakaan-kerja-luka-bakar-45-persen-dirujuk-ke-rsud-hm-rabaian</t>
+          <t>https://video.tribunnews.com/news/965254/sidang-kasus-korupsi-lpei-rp-992-miliar-bos-perusahaan-sawit-handoko-limaho-divonis-9-tahun-penjara</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Palpos</t>
+          <t>Tribun Video</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -9977,21 +9969,21 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46287.06454861111</v>
+        <v>46287.28171296296</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Buah Sawit Bukit Luik Desa Penagan Bangka Dijual ke PT</t>
+          <t>Viral Anggota DPRD Mempawah Bakar Kayu di Lahan Sebut untuk Ditanami Sawit, Polisi Turun Tangan</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>https://bangka.tribunnews.com/lokal/1697101/buah-sawit-bukit-luik-desa-penagan-bangka-dijual-ke-pt</t>
+          <t>https://wow.tribunnews.com/news/403534/viral-anggota-dprd-mempawah-bakar-kayu-di-lahan-sebut-untuk-ditanami-sawit-polisi-turun-tangan</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Bangkapos.com</t>
+          <t>TribunWow.com</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10024,21 +10016,21 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46287.5831712963</v>
+        <v>46287.70042824074</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Suami Diduga Selingkuh dengan Oknum PNS, Bos Sawit Menggala Bakal Lapor Polisi</t>
+          <t>Warga Desa Setia Jaya Desak Polres Muba Tindak Tegas Pengepul Sawit Ilegal</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>https://lampung.tribunnews.com/lampung/1218891/suami-diduga-selingkuh-dengan-oknum-pns-bos-sawit-menggala-bakal-lapor-polisi</t>
+          <t>https://www.kompasiana.com/taufik87687/6ab2b16534777c04414f2f72/warga-desa-setia-jaya-desak-polres-muba-tindak-tegas-pengepul-sawit-ilegal</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Tribunlampung.co.id</t>
+          <t>Kompasiana.com</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -10071,26 +10063,26 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46287.65401620371</v>
+        <v>46287.59789351852</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Bos Sawit Handoko Limaho Divonis 9 Tahun Penjara atas Kasus Korupsi LPEI Rp992 Miliar</t>
+          <t>Pemprov Sulbar Diduga Peras 8 Perusahaan Sawit Senilai Rp26,8 Miliar Berkedok Pajak Air Permukaan</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>https://www.tribunnews.com/nasional/7886343/bos-sawit-handoko-limaho-divonis-9-tahun-penjara-atas-kasus-korupsi-lpei-rp992-miliar</t>
+          <t>https://sulbar.bpk.go.id/pemprov-sulbar-diduga-peras-8-perusahaan-sawit-senilai-rp268-miliar-berkedok-pajak-air-permukaan/</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Tribunnews.com</t>
+          <t>sulbar.bpk.go.id</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Negatif</t>
+          <t>Netral</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -10118,21 +10110,21 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46287.39513888889</v>
+        <v>46287.58039351852</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BRIN Siapkan Inovasi Limbah Nanas dan Sawit untuk Tekstil dan UMKM</t>
+          <t>Agus Gumiwang resmikan Jalan Ratjih Natawidjaja di Sumedang</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>https://www.tribunnews.com/nasional/7886184/brin-siapkan-inovasi-limbah-nanas-dan-sawit-untuk-tekstil-dan-umkm</t>
+          <t>https://www.antaranews.com/berita/5753544/agus-gumiwang-resmikan-jalan-ratjih-natawidjaja-di-sumedang</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Tribunnews.com</t>
+          <t>ANTARA News</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -10140,21 +10132,25 @@
           <t>Positif</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MENTERI</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>sawit</t>
+          <t>pejabat_kemenperin, pejabat_presisi</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -10165,16 +10161,16 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46287.33842592593</v>
+        <v>46287.28634259259</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Negara Melawan Oligarki Fosil Melalui Sawit: Sosialisme Kedaulatan Energi Nasional</t>
+          <t>Mata Lokal Fest 2026 Hadirkan Cania Citta hingga Agus Gumiwang</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>https://www.tribunnews.com/tribunners/7886117/negara-melawan-oligarki-fosil-melalui-sawit-sosialisme-kedaulatan-energi-nasional</t>
+          <t>https://tangerang.tribunnews.com/news/61051/mata-lokal-fest-2026-hadirkan-cania-citta-hingga-agus-gumiwang</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10184,24 +10180,28 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Netral</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr"/>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MENTERI</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>sawit</t>
+          <t>pejabat_kemenperin</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -10212,43 +10212,51 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46287.68135416666</v>
+        <v>46287.28125</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Sidang Kasus Korupsi LPEI Rp 992 Miliar, Bos Perusahaan Sawit Handoko Limaho Divonis 9 Tahun Penjara</t>
+          <t>Indonesia Promotes Machinery Upgrades in Agro Industry</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>https://video.tribunnews.com/news/965254/sidang-kasus-korupsi-lpei-rp-992-miliar-bos-perusahaan-sawit-handoko-limaho-divonis-9-tahun-penjara</t>
+          <t>https://rri.co.id/voice-of-indonesia/business/2749293/indonesia-promotes-machinery-upgrades-in-agro-industry</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Tribun Video</t>
+          <t>rri.co.id</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Negatif</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>RR Citra Rapati</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>sawit</t>
+          <t>pejabat_kemenperin</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -10259,43 +10267,47 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46287.19850694444</v>
+        <v>46287.56944444445</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>BCA Sekuritas</t>
+          <t>Agus Gumiwang Resmikan Jalan Ratjih Natawidjaja di Sumedang, Kenang Jejak Pengabdian Tokoh Perempuan</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>https://bcasekuritas.co.id/latest-news/news/aprobi-pengembangan-bbn-berbasis-sawit-efektif-kurangi-impor-bbm</t>
+          <t>https://www.tribunnews.com/bisnis/7886303/agus-gumiwang-resmikan-jalan-ratjih-natawidjaja-di-sumedang-kenang-jejak-pengabdian-tokoh-perempuan</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>BCA Sekuritas</t>
+          <t>Tribunnews.com</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Netral</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr"/>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MENTERI</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>sawit</t>
+          <t>pejabat_kemenperin</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -10306,43 +10318,47 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46287.28171296296</v>
+        <v>46287.43575231481</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Viral Anggota DPRD Mempawah Bakar Kayu di Lahan Sebut untuk Ditanami Sawit, Polisi Turun Tangan</t>
+          <t>Gaikindo Auto Week 2026 Digelar di 10 Kota, Ini Jadwal dan Lokasinya</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>https://wow.tribunnews.com/news/403534/viral-anggota-dprd-mempawah-bakar-kayu-di-lahan-sebut-untuk-ditanami-sawit-polisi-turun-tangan</t>
+          <t>https://otomotif.bisnis.com/read/20260922/46/2006220/gaikindo-auto-week-2026-digelar-di-10-kota-ini-jadwal-dan-lokasinya</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>TribunWow.com</t>
+          <t>Bisnis.com - Otomotif</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Negatif</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr"/>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>sawit</t>
+          <t>pejabat_kemenperin</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -10353,43 +10369,47 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46287.70042824074</v>
+        <v>46287.43923611111</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Warga Desa Setia Jaya Desak Polres Muba Tindak Tegas Pengepul Sawit Ilegal</t>
+          <t>PermataBank Dorong Pembiayaan Kendaraan lewat Gaikindo Auto Week 2026</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>https://www.kompasiana.com/taufik87687/6ab2b16534777c04414f2f72/warga-desa-setia-jaya-desak-polres-muba-tindak-tegas-pengepul-sawit-ilegal</t>
+          <t>https://wartaekonomi.co.id/read636228/permatabank-dorong-pembiayaan-kendaraan-lewat-gaikindo-auto-week-2026</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Kompasiana.com</t>
+          <t>Warta Ekonomi</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Negatif</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr"/>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>sawit</t>
+          <t>pejabat_kemenperin</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -10400,21 +10420,21 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46287.59789351852</v>
+        <v>46287.43020833333</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Pemprov Sulbar Diduga Peras 8 Perusahaan Sawit Senilai Rp26,8 Miliar Berkedok Pajak Air Permukaan</t>
+          <t>Pertama di RI, Gaikindo Auto Week 2026 Digelar Serentak di 10 Kota, Berikut Lokasinya</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>https://sulbar.bpk.go.id/pemprov-sulbar-diduga-peras-8-perusahaan-sawit-senilai-rp268-miliar-berkedok-pajak-air-permukaan/</t>
+          <t>https://www.jpnn.com/news/pertama-di-ri-gaikindo-auto-week-2026-digelar-serentak-di-10-kota-berikut-lokasinya</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>sulbar.bpk.go.id</t>
+          <t>JPNN.com</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -10422,21 +10442,25 @@
           <t>Netral</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>sawit</t>
+          <t>pejabat_kemenperin</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -10447,21 +10471,21 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46287.58039351852</v>
+        <v>46287.27361111111</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Agus Gumiwang resmikan Jalan Ratjih Natawidjaja di Sumedang</t>
+          <t>Kemenperin Dorong Pelaku Industri Agro Modernisasi Mesin dan Peralatan Produksi</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5753544/agus-gumiwang-resmikan-jalan-ratjih-natawidjaja-di-sumedang</t>
+          <t>https://www.rctiplus.com/news/detail/terkini/5478118/kemenperin-dorong-pelaku-industri-agro-modernisasi-mesin-dan-peralatan-produksi?utm_source=mpi_widget&amp;utm_medium=referral&amp;utm_campaign=news_article_5478118</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ANTARA News</t>
+          <t>RCTI+</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -10474,7 +10498,11 @@
           <t>Agus Gumiwang Kartasasmita</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
       <c r="H213" t="inlineStr">
         <is>
           <t>MENTERI</t>
@@ -10487,7 +10515,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>pejabat_kemenperin</t>
+          <t>industri agro, pejabat_presisi</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -10498,21 +10526,21 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46287.28634259259</v>
+        <v>46287.59791666667</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mata Lokal Fest 2026 Hadirkan Cania Citta hingga Agus Gumiwang</t>
+          <t>Menperin Agus Gumiwang Resmikan Jalan Ratjih Natawidjaja, Kenang Jasa Sang Nenek di Sumedang</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>https://tangerang.tribunnews.com/news/61051/mata-lokal-fest-2026-hadirkan-cania-citta-hingga-agus-gumiwang</t>
+          <t>https://www.industry.co.id/read/156353/menperin-agus-gumiwang-resmikan-jalan-ratjih-natawidjaja-kenang-jasa-sang-nenek-di-sumedang</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Tribunnews.com</t>
+          <t>Industry.co.id</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -10538,7 +10566,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>pejabat_kemenperin</t>
+          <t>pejabat_presisi</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -10549,26 +10577,26 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46287.28125</v>
+        <v>46287.34375</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Indonesia Promotes Machinery Upgrades in Agro Industry</t>
+          <t>Kemenperin Buka Program Restrukturisasi Mesin Agro Via SIINas, Reimbursement Capai Rp1 Miliar Per Perusahaan</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>https://rri.co.id/voice-of-indonesia/business/2749293/indonesia-promotes-machinery-upgrades-in-agro-industry</t>
+          <t>https://www.industry.co.id/read/156345/kemenperin-buka-program-restrukturisasi-mesin-agro-via-siinas-reimbursement-capai-rp1-miliar-per-perusahaan</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>rri.co.id</t>
+          <t>Industry.co.id</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Netral</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -10593,7 +10621,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>pejabat_kemenperin</t>
+          <t>pejabat_presisi, pejabat_kemenperin</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -10604,21 +10632,21 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46287.56944444445</v>
+        <v>46287.27502314815</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Agus Gumiwang Resmikan Jalan Ratjih Natawidjaja di Sumedang, Kenang Jejak Pengabdian Tokoh Perempuan</t>
+          <t>Dorong Efisiensi dan Industri Hijau, Kemenperin Akselerasi Restrukturisasi Mesin Sektor Agro</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>https://www.tribunnews.com/bisnis/7886303/agus-gumiwang-resmikan-jalan-ratjih-natawidjaja-di-sumedang-kenang-jejak-pengabdian-tokoh-perempuan</t>
+          <t>https://majalahteras.com/dorong-efisiensi-dan-industri-hijau-kemenperin-akselerasi-restrukturisasi-mesin-sektor-agro/</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Tribunnews.com</t>
+          <t>Majalah Teras</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -10628,13 +10656,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
+          <t>RR Citra Rapati</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
           <t>Agus Gumiwang Kartasasmita</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
-          <t>MENTERI</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10644,7 +10676,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>pejabat_kemenperin</t>
+          <t>pejabat_presisi</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -10655,37 +10687,41 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46287.43575231481</v>
+        <v>46287.33680555555</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Gaikindo Auto Week 2026 Digelar di 10 Kota, Ini Jadwal dan Lokasinya</t>
+          <t>Menperin Agus Optimalkan PIDI 4.0 Jadi Hub Teknologi, Gandeng 65 Mitra Industri Dukung Mitigasi Bencana</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>https://otomotif.bisnis.com/read/20260922/46/2006220/gaikindo-auto-week-2026-digelar-di-10-kota-ini-jadwal-dan-lokasinya</t>
+          <t>https://www.industry.co.id/read/156344/menperin-agus-optimalkan-pidi-40-jadi-hub-teknologi-gandeng-65-mitra-industri-dukung-mitigasi-bencana</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Bisnis.com - Otomotif</t>
+          <t>Industry.co.id</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Positif</t>
+          <t>Negatif</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Putu Juli Ardika</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr"/>
+          <t>Faisol Riza</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>WAMEN</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10695,7 +10731,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>pejabat_kemenperin</t>
+          <t>pejabat_presisi</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -10706,21 +10742,21 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46287.43923611111</v>
+        <v>46287.42071759259</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PermataBank Dorong Pembiayaan Kendaraan lewat Gaikindo Auto Week 2026</t>
+          <t>Indonesia-Bulgaria Perkuat Kerja Sama Industri</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>https://wartaekonomi.co.id/read636228/permatabank-dorong-pembiayaan-kendaraan-lewat-gaikindo-auto-week-2026</t>
+          <t>https://tubasmedia.com/indonesia-bulgaria-perkuat-kerja-sama-industri/</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Warta Ekonomi</t>
+          <t>tubasmedia.com</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10730,13 +10766,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Putu Juli Ardika</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr"/>
+          <t>Faisol Riza</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Tri Supondy</t>
+        </is>
+      </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>WAMEN</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10746,7 +10786,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>pejabat_kemenperin</t>
+          <t>pejabat_presisi</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -10757,50 +10797,2241 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46287.43020833333</v>
+        <v>46287.58680555555</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Pertama di RI, Gaikindo Auto Week 2026 Digelar Serentak di 10 Kota, Berikut Lokasinya</t>
+          <t>Industri Hasil Hutan dan Perkebunan Didorong Perbarui Mesin Produksi</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>https://www.jpnn.com/news/pertama-di-ri-gaikindo-auto-week-2026-digelar-serentak-di-10-kota-berikut-lokasinya</t>
+          <t>https://www.panennews.com/industri/1683047197/industri-hasil-hutan-dan-perkebunan-didorong-perbarui-mesin-produksi</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>JPNN.com</t>
+          <t>panennews.com</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>RR Citra Rapati</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Faisol Riza</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46287.56184027778</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Menperin perkuat upaya pacu pengembangan industri di Sumedang</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5753511/menperin-perkuat-upaya-pacu-pengembangan-industri-di-sumedang</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>MENTERI</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46287.6061574074</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Unjuk Gigi di Festival Literasi Ciamis 2026, 18 Alumni Pelatihan Vokasi Racik Kopi Selevel Barista Kafe</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>https://fokusjabar.id/2026/09/22/unjuk-gigi-di-festival-literasi-ciamis-2026-18-alumni-pelatihan-vokasi-racik-kopi-selevel-barista-kafe/</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Fokus Jabar</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>MENTERI</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>kopi, pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46287.69488425926</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Shell Resmikan Pabrik Gemuk 12 Kiloton di Marunda Bekasi, Terbesar di Dunia</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>https://www.detik60.com/ekonomi/37017667138/shell-resmikan-pabrik-gemuk-12-kiloton-di-marunda-bekasi-terbesar-di-dunia</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Detik 60</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>MENTERI</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46287.49791666667</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>GAIKINDO Gelar Auto Week Serentak di 10 Kota, Bidik Dongkrak Penjualan Mobil Akhir Tahun</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>https://www.industry.co.id/read/156351/gaikindo-gelar-auto-week-serentak-di-10-kota-bidik-dongkrak-penjualan-mobil-akhir-tahun</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Industry.co.id</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46287.72638888889</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Industri Percetakan Indonesia Diproyeksi Tumbuh 3,39 Persen pada 2026</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>https://chatnews.id/industri-percetakan-indonesia-tumbuh-2026</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ChatNews.id</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46287.64662037037</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ALLPRINT INDONESIA 32 TAHUN: KETIKA CETAK HIJAB 35 RIBU, FOTO 100 TAHUN, DAN BESI DICETAK DI JIEXPO KEMAYORAN!</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>https://reportaseindonesia.com/2026/09/22/allprint-indonesia-32-tahun-ketika-cetak-hijab-35-ribu-foto-100-tahun-dan-besi-dicetak-di-jiexpo-kemayoran/</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>reportaseindonesia.com</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46287.42793981481</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Bukan Cuma Jakarta, Permata Bank GAIKINDO Auto Week 2026 Hadir Serentak di 10 Kota</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>https://autonesian.com/2026/09/bukan-cuma-jakarta-permata-bank-gaikindo-auto-week-2026-hadir-serentak-di-10-kota/</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>autonesian.com</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46287.39166666667</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Gaikindo Auto Week 2026 Digelar Serentak di 10 Kota, Pasar Otomotif Daerah Dibidik</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/otomotif/7886178/gaikindo-auto-week-2026-digelar-serentak-di-10-kota-pasar-otomotif-daerah-dibidik</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Tribunnews.com</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46287.49305555555</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Pameran Gaikindo Auto Week 2026 Digelar Serentak di 10 Kota, Ini Tanggal dan Lokasinya</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apakabar.co.id/ototekno/pameran-gaikindo-auto-week-2026-digelar-serentak-di-10-kota-ini-tanggal-dan-lokasinya/</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>APAKABAR</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46287.95833333334</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Permata Bank Gaikindo Auto Week 2026 Digelar Serntak di 10 Kota</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>https://tirto.id/permata-bank-gaikindo-auto-week-2026-digelar-serentak-di-10-kota-hDax</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Tirto.id</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
           <t>Netral</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>Putu Juli Ardika</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr">
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr">
         <is>
           <t>IA</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I229" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr">
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46287.54166666666</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>GAIKINDO Auto Week 2026 Ekspansi ke 10 Kota di Indonesia</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kabarbursa.com/otomotif/gaikindo-auto-week-2026-ekspansi-ke-10-kota-di-indonesia</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>kabarbursa.com</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46287.44097222222</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Rangsang Pertumbuhan Penjualan Kendaraan, Permata Bank Gaikindo Auto Week 2026 Hadir di 10 Kota</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mobilinanews.com/artikel/40561/Rangsang-Pertumbuhan-Penjualan-Kendaraan-Permata-Bank-Gaikindo-Auto-Week-2026-Hadir-di-10-Kota/</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Mobilinanews</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46287.59578703704</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>GAIKINDO Auto Week 2026: 10 Kota, 10 Hari, Satu Misi Penjualan Akhir Tahun</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>https://harianbisnis.id/2026/09/22/gaikindo-auto-week-2026-10-kota-10-hari-satu-misi-penjualan-akhir-tahun/</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>harianbisnis.id</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46287.54166666666</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Permata Bank GAIKINDO Auto Week 2026 Bikin Gebrakan Baru, Hadir Serentak Di 10 Kota Strategis Indonesia</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>https://www.otojatim.com/2026/09/permata-bank-gaikindo-auto-week-2026.html</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>otojatim.com</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46287.48005787037</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>GAIKINDO Auto Week 2026 Serentak 10 Kota Besar -</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>https://otoplasa.com/gaikindo-auto-week-2026-serentak-10-kota-besar/</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>otoplasa.com</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46287.61157407407</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Gaikindo Auto Week Gandeng Permata Bank, Hadirkan Pameran Otomotif Serentak di 10 Kota - Kabar Megapolitan</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kabarmegapolitan.id/bisnis/107917666786/gaikindo-auto-week-gandeng-permata-bank-hadirkan-pameran-otomotif-serentak-di-10-kota</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>kabarmegapolitan.id</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46287.74199074074</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Permata Bank GAIKINDO Auto Week 2026 Digelar Serentak di 10 Kota, Pameran Otomotif Kini Tak Lagi Terpusat</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>https://www.motorev.id/permata-bank-gaikindo-auto-week-2026-digelar-serentak-di-10-kota-pameran-otomotif-kini-tak-lagi-terpusat/</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>motorev.id</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Putu Juli Ardika</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>pejabat_presisi</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46287.26666666667</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>COCONUTRISE: Sulap Kelapa Mentah Jadi Minyak Kelapa</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>https://www.umy.ac.id/minyak-kelapa/</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>UMY</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>kelapa</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46287.48079861111</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>MUATAN TEPUNG TAPIOKA, TINGGI BANGET RAWAN MIRING..!!</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6iYodyR1yeo</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>JB TRANSPORT</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>tapioka</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46287.46835648148</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Produksi Rumput Laut Kabupaten Pangkep Tahun 2025 Capai 623.316 ton</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RuUB_i9qasU</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Pangkep TV</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>rumput laut</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46287.29428240741</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Dukung Produk Lokal! Dorongan Bangun Industri Olahan Rumput Laut Sendiri</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Jy_NG8Kkacg</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>FaktaMediaID</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>rumput laut</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46287.6547337963</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Apa Bahaya Makan Mi Instan Setiap Hari?</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>https://video.kompas.com/watch/1956365/apa-bahaya-makan-mi-instan-setiap-hari</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>video.kompas.com</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>mi instan</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46287.29166666666</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Pengujian Deterjen, Higiene, Kertas &amp; Pulp</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>https://www.eurofins.com/id-id/pengujian-produk-konsumen/deterjen-higiene-kertas-pulp/</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Eurofins Scientific</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>pulp</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46287.3625</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>PT. Surabaya Agung Industri Pulp &amp; Kertas Tbk [SAIP]</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>https://www.idnfinancials.com/nl/saip/pt-surabaya-agung-industri-pulp-kertas-tbk</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>IDNFinancials</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>pulp</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46287.84930555556</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>IMPLEMENTASI PRINSIP PRINSIP HUKUM EKONOMI SYARIAH PADA PELAKU USAHA MEBEL DI KABUPATEN PINRANG</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>https://repository.iainpare.ac.id/id/eprint/12882/</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Repository IAIN PAREPARE</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>mebel</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46287.89677083334</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>https://portal.tarakankota.go.id/data/daftar/cari?page=81</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Tarakan</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>mebel</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46287.29166666666</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Apa Itu Furniture? Ini Cara Memilih yang Tepat!</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>https://azko.id/inspiration/furniture-adalah</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>AZKO</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>furniture</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46287.32052083333</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HARGA KARET SGX – SICOM SELASA, 22 SEPTEMBER 2026 KKK 100% Rp42.183,-/Kg KKK 50% = Rp21.092,-/Kg</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PrEZi-rUMO8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Haji Rudi Arpian (HRA)</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>karet</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46287.0003125</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Harga kakao global, Selasa 22 September 2026 #hargacoklat #hargakakao #cacao</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qtqHNApIIZM</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Kakao Info</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>kakao</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46287.41685185185</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>“Nggak pakai kacang, kok cokelat tetap bisa berisi</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-GKpABYHIBg</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>GRI APAC</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>cokelat</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46287.44207175926</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Anggota DPR RI Angkat Bicara Soal Polemik Regulasi Tar &amp; Nikotin hingga Impor Tembakau</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTyfiwbWBwU</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Jurnal Plus</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>nikotin</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46287.67840277778</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Menjadi Inang Susu Putraku Sendiri Full Drama Chinese 2026 | New Drama All Episodes review and facts</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-RNlWFXL0qU</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Shosha Movies</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>susu</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46287.70833333334</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Gerai ibu hamil dan pemberian susu bumil kek</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>https://kampungkb.kemendukbangga.go.id/kampung/45439/intervensi/3098822/gerai-ibu-hamil-dan-pemberian-susu-bumil-kek</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Kampung Keluarga Berkualitas</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>susu</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46287.59630787037</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>FIRAL Vol 2 | Fakta Air Minum dalam Kemasan yang Bikin Geleng-Geleng</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LHEltTf8DqM</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Media Sabili</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>air minum dalam kemasan</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46287.40216435185</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Kopi Tangse: Saat Rasa Mengalahkan Popularitas | Dapu Kupi Qahwa</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RLMR9cFinb8</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Muhammad Hanif Hasballah</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>kopi</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46287.44833333333</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Amankan Pasar Utama CPO, Indonesia Percantik Pendekatan Bilateral | THE FUNDAMENTALS</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OcumwAVXS_Y</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>IDX CHANNEL</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>cpo</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46287.44556712963</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Upin ipin musing 18 minyak sawit</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=S_7WIO4Y2TI</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Nay animasi</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>minyak sawit</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46287.08366898148</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>EROPA PANIK? Tanpa Sawit Indonesia, Apa yang Terjadi?</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8dnq9qzz6vU</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Alisha Safiya Husna</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>minyak sawit</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46287.20851851852</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>BARAT GEMPAR😱‼️ SAWIT RI DISULAP JADI ENERGI, AMERIKA &amp; EROPA LANGSUNG ANTRE BELI</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AlpCBJQ2t0c</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>YudaMedia HD</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>minyak sawit</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46287.45835648148</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>B60: SIAPA YANG BAYAR? #B60 #Biodiesel #Sawit #Kelapasawit #MinyakSawit #BioEnergi #PetaniSawit</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hGETBIS6Boo</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Roni P</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>biodiesel</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46287.18857638889</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Sosialisasi Ketentuan Ekspor Produk Industri Agro dan Kimia</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MQMHUAs95-0</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Ditjen Daglu</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>industri agro</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46287.29166666666</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Konfirmasi Pajak PBJT atas Makanan dan Minuman</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>https://samarindakota.go.id/agenda/konfirmasi-pajak-pbjt-atas-makanan-dan-minuman-vwrag</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Portal Resmi Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>makanan dan minuman</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46287.61032407408</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Pengurangan Penggunaan Kantong Belanja Plastik Dan Wadah/Kemasan Makanan Dan Minuman</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>https://peraturan.bpk.go.id/Details/135236/permendikbud-no-23-tahun-2015</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>BPK RI</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>makanan dan minuman</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46287.25071759259</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Demo Ribuan Massa Duduki Lahan Perkebunan Sawit PT PAL Mesuji</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5N4LoynlxX0</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Lampung TV News</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>sawit</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46287.28505787037</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Cania Citta hingga Agus Gumiwang Bakal Berbagi Perspektif di Mata Lokal Fest 2026</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>https://sulbar.tribunnews.com/news/83403/cania-citta-hingga-agus-gumiwang-bakal-berbagi-perspektif-di-mata-lokal-fest-2026?page=2</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Tribun-sulbar.com</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Agus Gumiwang Kartasasmita</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>MENTERI</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
         <is>
           <t>pejabat_kemenperin</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="K264" t="inlineStr">
         <is>
           <t>RSS</t>
         </is>
@@ -11026,6 +13257,51 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId263"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
